--- a/lager-scanner/Lager_Vorlage.xlsx
+++ b/lager-scanner/Lager_Vorlage.xlsx
@@ -11,6 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stellplaetze" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protokoll" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lageruebersicht" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlanLayout" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagerplan" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +32,13 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="2">
@@ -52,14 +61,62 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00DDDDDD"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="00999999"/>
+        </left>
+        <right style="thin">
+          <color rgb="00999999"/>
+        </right>
+        <top style="thin">
+          <color rgb="00999999"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="00999999"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="00999999"/>
+        </left>
+        <right style="thin">
+          <color rgb="00999999"/>
+        </right>
+        <top style="thin">
+          <color rgb="00999999"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="00999999"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -26709,4 +26766,6701 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Hier die Stellplatz-Nummern so eintragen, wie das Lager wirklich aussieht (ab B2). Leere Zellen = Gang/Wand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" t="n">
+        <v>12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>13</v>
+      </c>
+      <c r="O3" t="n">
+        <v>14</v>
+      </c>
+      <c r="P3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>16</v>
+      </c>
+      <c r="R3" t="n">
+        <v>17</v>
+      </c>
+      <c r="S3" t="n">
+        <v>18</v>
+      </c>
+      <c r="T3" t="n">
+        <v>19</v>
+      </c>
+      <c r="U3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H5" t="n">
+        <v>27</v>
+      </c>
+      <c r="I5" t="n">
+        <v>28</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K5" t="n">
+        <v>30</v>
+      </c>
+      <c r="L5" t="n">
+        <v>31</v>
+      </c>
+      <c r="M5" t="n">
+        <v>32</v>
+      </c>
+      <c r="N5" t="n">
+        <v>33</v>
+      </c>
+      <c r="O5" t="n">
+        <v>34</v>
+      </c>
+      <c r="P5" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>36</v>
+      </c>
+      <c r="R5" t="n">
+        <v>37</v>
+      </c>
+      <c r="S5" t="n">
+        <v>38</v>
+      </c>
+      <c r="T5" t="n">
+        <v>39</v>
+      </c>
+      <c r="U5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AO41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="7" customWidth="1" min="21" max="21"/>
+    <col width="7" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="23"/>
+    <col width="7" customWidth="1" min="24" max="24"/>
+    <col width="7" customWidth="1" min="25" max="25"/>
+    <col width="7" customWidth="1" min="26" max="26"/>
+    <col width="7" customWidth="1" min="27" max="27"/>
+    <col width="7" customWidth="1" min="28" max="28"/>
+    <col width="7" customWidth="1" min="29" max="29"/>
+    <col width="7" customWidth="1" min="30" max="30"/>
+    <col width="7" customWidth="1" min="31" max="31"/>
+    <col width="7" customWidth="1" min="32" max="32"/>
+    <col width="7" customWidth="1" min="33" max="33"/>
+    <col width="7" customWidth="1" min="34" max="34"/>
+    <col width="7" customWidth="1" min="35" max="35"/>
+    <col width="7" customWidth="1" min="36" max="36"/>
+    <col width="7" customWidth="1" min="37" max="37"/>
+    <col width="7" customWidth="1" min="38" max="38"/>
+    <col width="7" customWidth="1" min="39" max="39"/>
+    <col width="7" customWidth="1" min="40" max="40"/>
+    <col width="7" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Lagerplan (nur lesen) – Platz / MN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="B2" s="4">
+        <f>IF(PlanLayout!B2="","",PlanLayout!B2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C2" s="4">
+        <f>IF(PlanLayout!C2="","",PlanLayout!C2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D2" s="4">
+        <f>IF(PlanLayout!D2="","",PlanLayout!D2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E2" s="4">
+        <f>IF(PlanLayout!E2="","",PlanLayout!E2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F2" s="4">
+        <f>IF(PlanLayout!F2="","",PlanLayout!F2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G2" s="4">
+        <f>IF(PlanLayout!G2="","",PlanLayout!G2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H2" s="4">
+        <f>IF(PlanLayout!H2="","",PlanLayout!H2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I2" s="4">
+        <f>IF(PlanLayout!I2="","",PlanLayout!I2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J2" s="4">
+        <f>IF(PlanLayout!J2="","",PlanLayout!J2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K2" s="4">
+        <f>IF(PlanLayout!K2="","",PlanLayout!K2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L2" s="4">
+        <f>IF(PlanLayout!L2="","",PlanLayout!L2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M2" s="4">
+        <f>IF(PlanLayout!M2="","",PlanLayout!M2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N2" s="4">
+        <f>IF(PlanLayout!N2="","",PlanLayout!N2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O2" s="4">
+        <f>IF(PlanLayout!O2="","",PlanLayout!O2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P2" s="4">
+        <f>IF(PlanLayout!P2="","",PlanLayout!P2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q2" s="4">
+        <f>IF(PlanLayout!Q2="","",PlanLayout!Q2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R2" s="4">
+        <f>IF(PlanLayout!R2="","",PlanLayout!R2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S2" s="4">
+        <f>IF(PlanLayout!S2="","",PlanLayout!S2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T2" s="4">
+        <f>IF(PlanLayout!T2="","",PlanLayout!T2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U2" s="4">
+        <f>IF(PlanLayout!U2="","",PlanLayout!U2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V2" s="4">
+        <f>IF(PlanLayout!V2="","",PlanLayout!V2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W2" s="4">
+        <f>IF(PlanLayout!W2="","",PlanLayout!W2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X2" s="4">
+        <f>IF(PlanLayout!X2="","",PlanLayout!X2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y2" s="4">
+        <f>IF(PlanLayout!Y2="","",PlanLayout!Y2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z2" s="4">
+        <f>IF(PlanLayout!Z2="","",PlanLayout!Z2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA2" s="4">
+        <f>IF(PlanLayout!AA2="","",PlanLayout!AA2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB2" s="4">
+        <f>IF(PlanLayout!AB2="","",PlanLayout!AB2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC2" s="4">
+        <f>IF(PlanLayout!AC2="","",PlanLayout!AC2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD2" s="4">
+        <f>IF(PlanLayout!AD2="","",PlanLayout!AD2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE2" s="4">
+        <f>IF(PlanLayout!AE2="","",PlanLayout!AE2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF2" s="4">
+        <f>IF(PlanLayout!AF2="","",PlanLayout!AF2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG2" s="4">
+        <f>IF(PlanLayout!AG2="","",PlanLayout!AG2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH2" s="4">
+        <f>IF(PlanLayout!AH2="","",PlanLayout!AH2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI2" s="4">
+        <f>IF(PlanLayout!AI2="","",PlanLayout!AI2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ2" s="4">
+        <f>IF(PlanLayout!AJ2="","",PlanLayout!AJ2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK2" s="4">
+        <f>IF(PlanLayout!AK2="","",PlanLayout!AK2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL2" s="4">
+        <f>IF(PlanLayout!AL2="","",PlanLayout!AL2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM2" s="4">
+        <f>IF(PlanLayout!AM2="","",PlanLayout!AM2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN2" s="4">
+        <f>IF(PlanLayout!AN2="","",PlanLayout!AN2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO2" s="4">
+        <f>IF(PlanLayout!AO2="","",PlanLayout!AO2&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO2,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO2,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO2,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO2,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="B3" s="4">
+        <f>IF(PlanLayout!B3="","",PlanLayout!B3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C3" s="4">
+        <f>IF(PlanLayout!C3="","",PlanLayout!C3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D3" s="4">
+        <f>IF(PlanLayout!D3="","",PlanLayout!D3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E3" s="4">
+        <f>IF(PlanLayout!E3="","",PlanLayout!E3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F3" s="4">
+        <f>IF(PlanLayout!F3="","",PlanLayout!F3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G3" s="4">
+        <f>IF(PlanLayout!G3="","",PlanLayout!G3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H3" s="4">
+        <f>IF(PlanLayout!H3="","",PlanLayout!H3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I3" s="4">
+        <f>IF(PlanLayout!I3="","",PlanLayout!I3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J3" s="4">
+        <f>IF(PlanLayout!J3="","",PlanLayout!J3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K3" s="4">
+        <f>IF(PlanLayout!K3="","",PlanLayout!K3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L3" s="4">
+        <f>IF(PlanLayout!L3="","",PlanLayout!L3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M3" s="4">
+        <f>IF(PlanLayout!M3="","",PlanLayout!M3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N3" s="4">
+        <f>IF(PlanLayout!N3="","",PlanLayout!N3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O3" s="4">
+        <f>IF(PlanLayout!O3="","",PlanLayout!O3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P3" s="4">
+        <f>IF(PlanLayout!P3="","",PlanLayout!P3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q3" s="4">
+        <f>IF(PlanLayout!Q3="","",PlanLayout!Q3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R3" s="4">
+        <f>IF(PlanLayout!R3="","",PlanLayout!R3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S3" s="4">
+        <f>IF(PlanLayout!S3="","",PlanLayout!S3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T3" s="4">
+        <f>IF(PlanLayout!T3="","",PlanLayout!T3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U3" s="4">
+        <f>IF(PlanLayout!U3="","",PlanLayout!U3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V3" s="4">
+        <f>IF(PlanLayout!V3="","",PlanLayout!V3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W3" s="4">
+        <f>IF(PlanLayout!W3="","",PlanLayout!W3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X3" s="4">
+        <f>IF(PlanLayout!X3="","",PlanLayout!X3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="4">
+        <f>IF(PlanLayout!Y3="","",PlanLayout!Y3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z3" s="4">
+        <f>IF(PlanLayout!Z3="","",PlanLayout!Z3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA3" s="4">
+        <f>IF(PlanLayout!AA3="","",PlanLayout!AA3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB3" s="4">
+        <f>IF(PlanLayout!AB3="","",PlanLayout!AB3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC3" s="4">
+        <f>IF(PlanLayout!AC3="","",PlanLayout!AC3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD3" s="4">
+        <f>IF(PlanLayout!AD3="","",PlanLayout!AD3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE3" s="4">
+        <f>IF(PlanLayout!AE3="","",PlanLayout!AE3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF3" s="4">
+        <f>IF(PlanLayout!AF3="","",PlanLayout!AF3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG3" s="4">
+        <f>IF(PlanLayout!AG3="","",PlanLayout!AG3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH3" s="4">
+        <f>IF(PlanLayout!AH3="","",PlanLayout!AH3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI3" s="4">
+        <f>IF(PlanLayout!AI3="","",PlanLayout!AI3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ3" s="4">
+        <f>IF(PlanLayout!AJ3="","",PlanLayout!AJ3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK3" s="4">
+        <f>IF(PlanLayout!AK3="","",PlanLayout!AK3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL3" s="4">
+        <f>IF(PlanLayout!AL3="","",PlanLayout!AL3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM3" s="4">
+        <f>IF(PlanLayout!AM3="","",PlanLayout!AM3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN3" s="4">
+        <f>IF(PlanLayout!AN3="","",PlanLayout!AN3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO3" s="4">
+        <f>IF(PlanLayout!AO3="","",PlanLayout!AO3&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO3,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO3,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO3,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO3,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="B4" s="4">
+        <f>IF(PlanLayout!B4="","",PlanLayout!B4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C4" s="4">
+        <f>IF(PlanLayout!C4="","",PlanLayout!C4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D4" s="4">
+        <f>IF(PlanLayout!D4="","",PlanLayout!D4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E4" s="4">
+        <f>IF(PlanLayout!E4="","",PlanLayout!E4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F4" s="4">
+        <f>IF(PlanLayout!F4="","",PlanLayout!F4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G4" s="4">
+        <f>IF(PlanLayout!G4="","",PlanLayout!G4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H4" s="4">
+        <f>IF(PlanLayout!H4="","",PlanLayout!H4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I4" s="4">
+        <f>IF(PlanLayout!I4="","",PlanLayout!I4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J4" s="4">
+        <f>IF(PlanLayout!J4="","",PlanLayout!J4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K4" s="4">
+        <f>IF(PlanLayout!K4="","",PlanLayout!K4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L4" s="4">
+        <f>IF(PlanLayout!L4="","",PlanLayout!L4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M4" s="4">
+        <f>IF(PlanLayout!M4="","",PlanLayout!M4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N4" s="4">
+        <f>IF(PlanLayout!N4="","",PlanLayout!N4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O4" s="4">
+        <f>IF(PlanLayout!O4="","",PlanLayout!O4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P4" s="4">
+        <f>IF(PlanLayout!P4="","",PlanLayout!P4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q4" s="4">
+        <f>IF(PlanLayout!Q4="","",PlanLayout!Q4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R4" s="4">
+        <f>IF(PlanLayout!R4="","",PlanLayout!R4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S4" s="4">
+        <f>IF(PlanLayout!S4="","",PlanLayout!S4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T4" s="4">
+        <f>IF(PlanLayout!T4="","",PlanLayout!T4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U4" s="4">
+        <f>IF(PlanLayout!U4="","",PlanLayout!U4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V4" s="4">
+        <f>IF(PlanLayout!V4="","",PlanLayout!V4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W4" s="4">
+        <f>IF(PlanLayout!W4="","",PlanLayout!W4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X4" s="4">
+        <f>IF(PlanLayout!X4="","",PlanLayout!X4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y4" s="4">
+        <f>IF(PlanLayout!Y4="","",PlanLayout!Y4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z4" s="4">
+        <f>IF(PlanLayout!Z4="","",PlanLayout!Z4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA4" s="4">
+        <f>IF(PlanLayout!AA4="","",PlanLayout!AA4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB4" s="4">
+        <f>IF(PlanLayout!AB4="","",PlanLayout!AB4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC4" s="4">
+        <f>IF(PlanLayout!AC4="","",PlanLayout!AC4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD4" s="4">
+        <f>IF(PlanLayout!AD4="","",PlanLayout!AD4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE4" s="4">
+        <f>IF(PlanLayout!AE4="","",PlanLayout!AE4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF4" s="4">
+        <f>IF(PlanLayout!AF4="","",PlanLayout!AF4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG4" s="4">
+        <f>IF(PlanLayout!AG4="","",PlanLayout!AG4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH4" s="4">
+        <f>IF(PlanLayout!AH4="","",PlanLayout!AH4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI4" s="4">
+        <f>IF(PlanLayout!AI4="","",PlanLayout!AI4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ4" s="4">
+        <f>IF(PlanLayout!AJ4="","",PlanLayout!AJ4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK4" s="4">
+        <f>IF(PlanLayout!AK4="","",PlanLayout!AK4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL4" s="4">
+        <f>IF(PlanLayout!AL4="","",PlanLayout!AL4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM4" s="4">
+        <f>IF(PlanLayout!AM4="","",PlanLayout!AM4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN4" s="4">
+        <f>IF(PlanLayout!AN4="","",PlanLayout!AN4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO4" s="4">
+        <f>IF(PlanLayout!AO4="","",PlanLayout!AO4&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO4,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO4,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO4,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO4,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="4">
+        <f>IF(PlanLayout!B5="","",PlanLayout!B5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IF(PlanLayout!C5="","",PlanLayout!C5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IF(PlanLayout!D5="","",PlanLayout!D5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IF(PlanLayout!E5="","",PlanLayout!E5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F5" s="4">
+        <f>IF(PlanLayout!F5="","",PlanLayout!F5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G5" s="4">
+        <f>IF(PlanLayout!G5="","",PlanLayout!G5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H5" s="4">
+        <f>IF(PlanLayout!H5="","",PlanLayout!H5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I5" s="4">
+        <f>IF(PlanLayout!I5="","",PlanLayout!I5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J5" s="4">
+        <f>IF(PlanLayout!J5="","",PlanLayout!J5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K5" s="4">
+        <f>IF(PlanLayout!K5="","",PlanLayout!K5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L5" s="4">
+        <f>IF(PlanLayout!L5="","",PlanLayout!L5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M5" s="4">
+        <f>IF(PlanLayout!M5="","",PlanLayout!M5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N5" s="4">
+        <f>IF(PlanLayout!N5="","",PlanLayout!N5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O5" s="4">
+        <f>IF(PlanLayout!O5="","",PlanLayout!O5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P5" s="4">
+        <f>IF(PlanLayout!P5="","",PlanLayout!P5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="4">
+        <f>IF(PlanLayout!Q5="","",PlanLayout!Q5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R5" s="4">
+        <f>IF(PlanLayout!R5="","",PlanLayout!R5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S5" s="4">
+        <f>IF(PlanLayout!S5="","",PlanLayout!S5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T5" s="4">
+        <f>IF(PlanLayout!T5="","",PlanLayout!T5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U5" s="4">
+        <f>IF(PlanLayout!U5="","",PlanLayout!U5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V5" s="4">
+        <f>IF(PlanLayout!V5="","",PlanLayout!V5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W5" s="4">
+        <f>IF(PlanLayout!W5="","",PlanLayout!W5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X5" s="4">
+        <f>IF(PlanLayout!X5="","",PlanLayout!X5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y5" s="4">
+        <f>IF(PlanLayout!Y5="","",PlanLayout!Y5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z5" s="4">
+        <f>IF(PlanLayout!Z5="","",PlanLayout!Z5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA5" s="4">
+        <f>IF(PlanLayout!AA5="","",PlanLayout!AA5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB5" s="4">
+        <f>IF(PlanLayout!AB5="","",PlanLayout!AB5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC5" s="4">
+        <f>IF(PlanLayout!AC5="","",PlanLayout!AC5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD5" s="4">
+        <f>IF(PlanLayout!AD5="","",PlanLayout!AD5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE5" s="4">
+        <f>IF(PlanLayout!AE5="","",PlanLayout!AE5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF5" s="4">
+        <f>IF(PlanLayout!AF5="","",PlanLayout!AF5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG5" s="4">
+        <f>IF(PlanLayout!AG5="","",PlanLayout!AG5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH5" s="4">
+        <f>IF(PlanLayout!AH5="","",PlanLayout!AH5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI5" s="4">
+        <f>IF(PlanLayout!AI5="","",PlanLayout!AI5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="4">
+        <f>IF(PlanLayout!AJ5="","",PlanLayout!AJ5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK5" s="4">
+        <f>IF(PlanLayout!AK5="","",PlanLayout!AK5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL5" s="4">
+        <f>IF(PlanLayout!AL5="","",PlanLayout!AL5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM5" s="4">
+        <f>IF(PlanLayout!AM5="","",PlanLayout!AM5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN5" s="4">
+        <f>IF(PlanLayout!AN5="","",PlanLayout!AN5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO5" s="4">
+        <f>IF(PlanLayout!AO5="","",PlanLayout!AO5&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO5,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO5,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO5,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO5,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="B6" s="4">
+        <f>IF(PlanLayout!B6="","",PlanLayout!B6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C6" s="4">
+        <f>IF(PlanLayout!C6="","",PlanLayout!C6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D6" s="4">
+        <f>IF(PlanLayout!D6="","",PlanLayout!D6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E6" s="4">
+        <f>IF(PlanLayout!E6="","",PlanLayout!E6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F6" s="4">
+        <f>IF(PlanLayout!F6="","",PlanLayout!F6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G6" s="4">
+        <f>IF(PlanLayout!G6="","",PlanLayout!G6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H6" s="4">
+        <f>IF(PlanLayout!H6="","",PlanLayout!H6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I6" s="4">
+        <f>IF(PlanLayout!I6="","",PlanLayout!I6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J6" s="4">
+        <f>IF(PlanLayout!J6="","",PlanLayout!J6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K6" s="4">
+        <f>IF(PlanLayout!K6="","",PlanLayout!K6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L6" s="4">
+        <f>IF(PlanLayout!L6="","",PlanLayout!L6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M6" s="4">
+        <f>IF(PlanLayout!M6="","",PlanLayout!M6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N6" s="4">
+        <f>IF(PlanLayout!N6="","",PlanLayout!N6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O6" s="4">
+        <f>IF(PlanLayout!O6="","",PlanLayout!O6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P6" s="4">
+        <f>IF(PlanLayout!P6="","",PlanLayout!P6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="4">
+        <f>IF(PlanLayout!Q6="","",PlanLayout!Q6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R6" s="4">
+        <f>IF(PlanLayout!R6="","",PlanLayout!R6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S6" s="4">
+        <f>IF(PlanLayout!S6="","",PlanLayout!S6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T6" s="4">
+        <f>IF(PlanLayout!T6="","",PlanLayout!T6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U6" s="4">
+        <f>IF(PlanLayout!U6="","",PlanLayout!U6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V6" s="4">
+        <f>IF(PlanLayout!V6="","",PlanLayout!V6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W6" s="4">
+        <f>IF(PlanLayout!W6="","",PlanLayout!W6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X6" s="4">
+        <f>IF(PlanLayout!X6="","",PlanLayout!X6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y6" s="4">
+        <f>IF(PlanLayout!Y6="","",PlanLayout!Y6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z6" s="4">
+        <f>IF(PlanLayout!Z6="","",PlanLayout!Z6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA6" s="4">
+        <f>IF(PlanLayout!AA6="","",PlanLayout!AA6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB6" s="4">
+        <f>IF(PlanLayout!AB6="","",PlanLayout!AB6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC6" s="4">
+        <f>IF(PlanLayout!AC6="","",PlanLayout!AC6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD6" s="4">
+        <f>IF(PlanLayout!AD6="","",PlanLayout!AD6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE6" s="4">
+        <f>IF(PlanLayout!AE6="","",PlanLayout!AE6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF6" s="4">
+        <f>IF(PlanLayout!AF6="","",PlanLayout!AF6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG6" s="4">
+        <f>IF(PlanLayout!AG6="","",PlanLayout!AG6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH6" s="4">
+        <f>IF(PlanLayout!AH6="","",PlanLayout!AH6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI6" s="4">
+        <f>IF(PlanLayout!AI6="","",PlanLayout!AI6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="4">
+        <f>IF(PlanLayout!AJ6="","",PlanLayout!AJ6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK6" s="4">
+        <f>IF(PlanLayout!AK6="","",PlanLayout!AK6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL6" s="4">
+        <f>IF(PlanLayout!AL6="","",PlanLayout!AL6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM6" s="4">
+        <f>IF(PlanLayout!AM6="","",PlanLayout!AM6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN6" s="4">
+        <f>IF(PlanLayout!AN6="","",PlanLayout!AN6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO6" s="4">
+        <f>IF(PlanLayout!AO6="","",PlanLayout!AO6&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO6,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO6,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO6,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO6,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="B7" s="4">
+        <f>IF(PlanLayout!B7="","",PlanLayout!B7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IF(PlanLayout!C7="","",PlanLayout!C7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IF(PlanLayout!D7="","",PlanLayout!D7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IF(PlanLayout!E7="","",PlanLayout!E7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F7" s="4">
+        <f>IF(PlanLayout!F7="","",PlanLayout!F7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G7" s="4">
+        <f>IF(PlanLayout!G7="","",PlanLayout!G7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H7" s="4">
+        <f>IF(PlanLayout!H7="","",PlanLayout!H7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I7" s="4">
+        <f>IF(PlanLayout!I7="","",PlanLayout!I7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J7" s="4">
+        <f>IF(PlanLayout!J7="","",PlanLayout!J7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K7" s="4">
+        <f>IF(PlanLayout!K7="","",PlanLayout!K7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L7" s="4">
+        <f>IF(PlanLayout!L7="","",PlanLayout!L7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M7" s="4">
+        <f>IF(PlanLayout!M7="","",PlanLayout!M7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N7" s="4">
+        <f>IF(PlanLayout!N7="","",PlanLayout!N7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O7" s="4">
+        <f>IF(PlanLayout!O7="","",PlanLayout!O7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P7" s="4">
+        <f>IF(PlanLayout!P7="","",PlanLayout!P7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="4">
+        <f>IF(PlanLayout!Q7="","",PlanLayout!Q7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R7" s="4">
+        <f>IF(PlanLayout!R7="","",PlanLayout!R7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S7" s="4">
+        <f>IF(PlanLayout!S7="","",PlanLayout!S7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T7" s="4">
+        <f>IF(PlanLayout!T7="","",PlanLayout!T7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U7" s="4">
+        <f>IF(PlanLayout!U7="","",PlanLayout!U7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V7" s="4">
+        <f>IF(PlanLayout!V7="","",PlanLayout!V7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W7" s="4">
+        <f>IF(PlanLayout!W7="","",PlanLayout!W7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X7" s="4">
+        <f>IF(PlanLayout!X7="","",PlanLayout!X7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y7" s="4">
+        <f>IF(PlanLayout!Y7="","",PlanLayout!Y7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z7" s="4">
+        <f>IF(PlanLayout!Z7="","",PlanLayout!Z7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA7" s="4">
+        <f>IF(PlanLayout!AA7="","",PlanLayout!AA7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB7" s="4">
+        <f>IF(PlanLayout!AB7="","",PlanLayout!AB7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC7" s="4">
+        <f>IF(PlanLayout!AC7="","",PlanLayout!AC7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD7" s="4">
+        <f>IF(PlanLayout!AD7="","",PlanLayout!AD7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE7" s="4">
+        <f>IF(PlanLayout!AE7="","",PlanLayout!AE7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF7" s="4">
+        <f>IF(PlanLayout!AF7="","",PlanLayout!AF7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG7" s="4">
+        <f>IF(PlanLayout!AG7="","",PlanLayout!AG7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH7" s="4">
+        <f>IF(PlanLayout!AH7="","",PlanLayout!AH7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI7" s="4">
+        <f>IF(PlanLayout!AI7="","",PlanLayout!AI7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="4">
+        <f>IF(PlanLayout!AJ7="","",PlanLayout!AJ7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK7" s="4">
+        <f>IF(PlanLayout!AK7="","",PlanLayout!AK7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL7" s="4">
+        <f>IF(PlanLayout!AL7="","",PlanLayout!AL7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM7" s="4">
+        <f>IF(PlanLayout!AM7="","",PlanLayout!AM7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN7" s="4">
+        <f>IF(PlanLayout!AN7="","",PlanLayout!AN7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO7" s="4">
+        <f>IF(PlanLayout!AO7="","",PlanLayout!AO7&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO7,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO7,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO7,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO7,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="B8" s="4">
+        <f>IF(PlanLayout!B8="","",PlanLayout!B8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C8" s="4">
+        <f>IF(PlanLayout!C8="","",PlanLayout!C8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D8" s="4">
+        <f>IF(PlanLayout!D8="","",PlanLayout!D8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E8" s="4">
+        <f>IF(PlanLayout!E8="","",PlanLayout!E8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F8" s="4">
+        <f>IF(PlanLayout!F8="","",PlanLayout!F8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G8" s="4">
+        <f>IF(PlanLayout!G8="","",PlanLayout!G8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H8" s="4">
+        <f>IF(PlanLayout!H8="","",PlanLayout!H8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I8" s="4">
+        <f>IF(PlanLayout!I8="","",PlanLayout!I8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J8" s="4">
+        <f>IF(PlanLayout!J8="","",PlanLayout!J8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K8" s="4">
+        <f>IF(PlanLayout!K8="","",PlanLayout!K8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L8" s="4">
+        <f>IF(PlanLayout!L8="","",PlanLayout!L8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M8" s="4">
+        <f>IF(PlanLayout!M8="","",PlanLayout!M8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N8" s="4">
+        <f>IF(PlanLayout!N8="","",PlanLayout!N8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O8" s="4">
+        <f>IF(PlanLayout!O8="","",PlanLayout!O8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P8" s="4">
+        <f>IF(PlanLayout!P8="","",PlanLayout!P8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="4">
+        <f>IF(PlanLayout!Q8="","",PlanLayout!Q8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R8" s="4">
+        <f>IF(PlanLayout!R8="","",PlanLayout!R8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S8" s="4">
+        <f>IF(PlanLayout!S8="","",PlanLayout!S8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T8" s="4">
+        <f>IF(PlanLayout!T8="","",PlanLayout!T8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U8" s="4">
+        <f>IF(PlanLayout!U8="","",PlanLayout!U8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V8" s="4">
+        <f>IF(PlanLayout!V8="","",PlanLayout!V8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W8" s="4">
+        <f>IF(PlanLayout!W8="","",PlanLayout!W8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X8" s="4">
+        <f>IF(PlanLayout!X8="","",PlanLayout!X8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y8" s="4">
+        <f>IF(PlanLayout!Y8="","",PlanLayout!Y8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z8" s="4">
+        <f>IF(PlanLayout!Z8="","",PlanLayout!Z8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA8" s="4">
+        <f>IF(PlanLayout!AA8="","",PlanLayout!AA8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB8" s="4">
+        <f>IF(PlanLayout!AB8="","",PlanLayout!AB8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC8" s="4">
+        <f>IF(PlanLayout!AC8="","",PlanLayout!AC8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD8" s="4">
+        <f>IF(PlanLayout!AD8="","",PlanLayout!AD8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE8" s="4">
+        <f>IF(PlanLayout!AE8="","",PlanLayout!AE8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF8" s="4">
+        <f>IF(PlanLayout!AF8="","",PlanLayout!AF8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG8" s="4">
+        <f>IF(PlanLayout!AG8="","",PlanLayout!AG8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH8" s="4">
+        <f>IF(PlanLayout!AH8="","",PlanLayout!AH8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI8" s="4">
+        <f>IF(PlanLayout!AI8="","",PlanLayout!AI8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="4">
+        <f>IF(PlanLayout!AJ8="","",PlanLayout!AJ8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK8" s="4">
+        <f>IF(PlanLayout!AK8="","",PlanLayout!AK8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL8" s="4">
+        <f>IF(PlanLayout!AL8="","",PlanLayout!AL8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM8" s="4">
+        <f>IF(PlanLayout!AM8="","",PlanLayout!AM8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN8" s="4">
+        <f>IF(PlanLayout!AN8="","",PlanLayout!AN8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO8" s="4">
+        <f>IF(PlanLayout!AO8="","",PlanLayout!AO8&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO8,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO8,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO8,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO8,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="B9" s="4">
+        <f>IF(PlanLayout!B9="","",PlanLayout!B9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C9" s="4">
+        <f>IF(PlanLayout!C9="","",PlanLayout!C9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D9" s="4">
+        <f>IF(PlanLayout!D9="","",PlanLayout!D9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E9" s="4">
+        <f>IF(PlanLayout!E9="","",PlanLayout!E9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F9" s="4">
+        <f>IF(PlanLayout!F9="","",PlanLayout!F9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G9" s="4">
+        <f>IF(PlanLayout!G9="","",PlanLayout!G9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H9" s="4">
+        <f>IF(PlanLayout!H9="","",PlanLayout!H9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I9" s="4">
+        <f>IF(PlanLayout!I9="","",PlanLayout!I9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J9" s="4">
+        <f>IF(PlanLayout!J9="","",PlanLayout!J9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K9" s="4">
+        <f>IF(PlanLayout!K9="","",PlanLayout!K9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L9" s="4">
+        <f>IF(PlanLayout!L9="","",PlanLayout!L9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M9" s="4">
+        <f>IF(PlanLayout!M9="","",PlanLayout!M9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N9" s="4">
+        <f>IF(PlanLayout!N9="","",PlanLayout!N9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O9" s="4">
+        <f>IF(PlanLayout!O9="","",PlanLayout!O9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P9" s="4">
+        <f>IF(PlanLayout!P9="","",PlanLayout!P9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="4">
+        <f>IF(PlanLayout!Q9="","",PlanLayout!Q9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R9" s="4">
+        <f>IF(PlanLayout!R9="","",PlanLayout!R9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S9" s="4">
+        <f>IF(PlanLayout!S9="","",PlanLayout!S9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T9" s="4">
+        <f>IF(PlanLayout!T9="","",PlanLayout!T9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U9" s="4">
+        <f>IF(PlanLayout!U9="","",PlanLayout!U9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V9" s="4">
+        <f>IF(PlanLayout!V9="","",PlanLayout!V9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W9" s="4">
+        <f>IF(PlanLayout!W9="","",PlanLayout!W9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X9" s="4">
+        <f>IF(PlanLayout!X9="","",PlanLayout!X9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y9" s="4">
+        <f>IF(PlanLayout!Y9="","",PlanLayout!Y9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z9" s="4">
+        <f>IF(PlanLayout!Z9="","",PlanLayout!Z9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA9" s="4">
+        <f>IF(PlanLayout!AA9="","",PlanLayout!AA9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB9" s="4">
+        <f>IF(PlanLayout!AB9="","",PlanLayout!AB9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC9" s="4">
+        <f>IF(PlanLayout!AC9="","",PlanLayout!AC9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD9" s="4">
+        <f>IF(PlanLayout!AD9="","",PlanLayout!AD9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE9" s="4">
+        <f>IF(PlanLayout!AE9="","",PlanLayout!AE9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF9" s="4">
+        <f>IF(PlanLayout!AF9="","",PlanLayout!AF9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG9" s="4">
+        <f>IF(PlanLayout!AG9="","",PlanLayout!AG9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH9" s="4">
+        <f>IF(PlanLayout!AH9="","",PlanLayout!AH9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI9" s="4">
+        <f>IF(PlanLayout!AI9="","",PlanLayout!AI9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="4">
+        <f>IF(PlanLayout!AJ9="","",PlanLayout!AJ9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK9" s="4">
+        <f>IF(PlanLayout!AK9="","",PlanLayout!AK9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL9" s="4">
+        <f>IF(PlanLayout!AL9="","",PlanLayout!AL9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM9" s="4">
+        <f>IF(PlanLayout!AM9="","",PlanLayout!AM9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN9" s="4">
+        <f>IF(PlanLayout!AN9="","",PlanLayout!AN9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO9" s="4">
+        <f>IF(PlanLayout!AO9="","",PlanLayout!AO9&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO9,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO9,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO9,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO9,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="B10" s="4">
+        <f>IF(PlanLayout!B10="","",PlanLayout!B10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IF(PlanLayout!C10="","",PlanLayout!C10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IF(PlanLayout!D10="","",PlanLayout!D10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IF(PlanLayout!E10="","",PlanLayout!E10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F10" s="4">
+        <f>IF(PlanLayout!F10="","",PlanLayout!F10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="4">
+        <f>IF(PlanLayout!G10="","",PlanLayout!G10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H10" s="4">
+        <f>IF(PlanLayout!H10="","",PlanLayout!H10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I10" s="4">
+        <f>IF(PlanLayout!I10="","",PlanLayout!I10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J10" s="4">
+        <f>IF(PlanLayout!J10="","",PlanLayout!J10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K10" s="4">
+        <f>IF(PlanLayout!K10="","",PlanLayout!K10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L10" s="4">
+        <f>IF(PlanLayout!L10="","",PlanLayout!L10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M10" s="4">
+        <f>IF(PlanLayout!M10="","",PlanLayout!M10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N10" s="4">
+        <f>IF(PlanLayout!N10="","",PlanLayout!N10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O10" s="4">
+        <f>IF(PlanLayout!O10="","",PlanLayout!O10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P10" s="4">
+        <f>IF(PlanLayout!P10="","",PlanLayout!P10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="4">
+        <f>IF(PlanLayout!Q10="","",PlanLayout!Q10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R10" s="4">
+        <f>IF(PlanLayout!R10="","",PlanLayout!R10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S10" s="4">
+        <f>IF(PlanLayout!S10="","",PlanLayout!S10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T10" s="4">
+        <f>IF(PlanLayout!T10="","",PlanLayout!T10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U10" s="4">
+        <f>IF(PlanLayout!U10="","",PlanLayout!U10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V10" s="4">
+        <f>IF(PlanLayout!V10="","",PlanLayout!V10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W10" s="4">
+        <f>IF(PlanLayout!W10="","",PlanLayout!W10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X10" s="4">
+        <f>IF(PlanLayout!X10="","",PlanLayout!X10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y10" s="4">
+        <f>IF(PlanLayout!Y10="","",PlanLayout!Y10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z10" s="4">
+        <f>IF(PlanLayout!Z10="","",PlanLayout!Z10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA10" s="4">
+        <f>IF(PlanLayout!AA10="","",PlanLayout!AA10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB10" s="4">
+        <f>IF(PlanLayout!AB10="","",PlanLayout!AB10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC10" s="4">
+        <f>IF(PlanLayout!AC10="","",PlanLayout!AC10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD10" s="4">
+        <f>IF(PlanLayout!AD10="","",PlanLayout!AD10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE10" s="4">
+        <f>IF(PlanLayout!AE10="","",PlanLayout!AE10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF10" s="4">
+        <f>IF(PlanLayout!AF10="","",PlanLayout!AF10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG10" s="4">
+        <f>IF(PlanLayout!AG10="","",PlanLayout!AG10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH10" s="4">
+        <f>IF(PlanLayout!AH10="","",PlanLayout!AH10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI10" s="4">
+        <f>IF(PlanLayout!AI10="","",PlanLayout!AI10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="4">
+        <f>IF(PlanLayout!AJ10="","",PlanLayout!AJ10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK10" s="4">
+        <f>IF(PlanLayout!AK10="","",PlanLayout!AK10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL10" s="4">
+        <f>IF(PlanLayout!AL10="","",PlanLayout!AL10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM10" s="4">
+        <f>IF(PlanLayout!AM10="","",PlanLayout!AM10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN10" s="4">
+        <f>IF(PlanLayout!AN10="","",PlanLayout!AN10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO10" s="4">
+        <f>IF(PlanLayout!AO10="","",PlanLayout!AO10&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO10,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO10,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO10,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO10,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" s="4">
+        <f>IF(PlanLayout!B11="","",PlanLayout!B11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C11" s="4">
+        <f>IF(PlanLayout!C11="","",PlanLayout!C11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D11" s="4">
+        <f>IF(PlanLayout!D11="","",PlanLayout!D11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E11" s="4">
+        <f>IF(PlanLayout!E11="","",PlanLayout!E11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F11" s="4">
+        <f>IF(PlanLayout!F11="","",PlanLayout!F11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G11" s="4">
+        <f>IF(PlanLayout!G11="","",PlanLayout!G11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H11" s="4">
+        <f>IF(PlanLayout!H11="","",PlanLayout!H11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I11" s="4">
+        <f>IF(PlanLayout!I11="","",PlanLayout!I11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J11" s="4">
+        <f>IF(PlanLayout!J11="","",PlanLayout!J11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K11" s="4">
+        <f>IF(PlanLayout!K11="","",PlanLayout!K11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L11" s="4">
+        <f>IF(PlanLayout!L11="","",PlanLayout!L11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M11" s="4">
+        <f>IF(PlanLayout!M11="","",PlanLayout!M11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N11" s="4">
+        <f>IF(PlanLayout!N11="","",PlanLayout!N11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O11" s="4">
+        <f>IF(PlanLayout!O11="","",PlanLayout!O11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P11" s="4">
+        <f>IF(PlanLayout!P11="","",PlanLayout!P11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="4">
+        <f>IF(PlanLayout!Q11="","",PlanLayout!Q11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R11" s="4">
+        <f>IF(PlanLayout!R11="","",PlanLayout!R11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S11" s="4">
+        <f>IF(PlanLayout!S11="","",PlanLayout!S11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T11" s="4">
+        <f>IF(PlanLayout!T11="","",PlanLayout!T11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U11" s="4">
+        <f>IF(PlanLayout!U11="","",PlanLayout!U11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V11" s="4">
+        <f>IF(PlanLayout!V11="","",PlanLayout!V11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W11" s="4">
+        <f>IF(PlanLayout!W11="","",PlanLayout!W11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X11" s="4">
+        <f>IF(PlanLayout!X11="","",PlanLayout!X11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y11" s="4">
+        <f>IF(PlanLayout!Y11="","",PlanLayout!Y11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z11" s="4">
+        <f>IF(PlanLayout!Z11="","",PlanLayout!Z11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA11" s="4">
+        <f>IF(PlanLayout!AA11="","",PlanLayout!AA11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB11" s="4">
+        <f>IF(PlanLayout!AB11="","",PlanLayout!AB11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC11" s="4">
+        <f>IF(PlanLayout!AC11="","",PlanLayout!AC11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD11" s="4">
+        <f>IF(PlanLayout!AD11="","",PlanLayout!AD11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE11" s="4">
+        <f>IF(PlanLayout!AE11="","",PlanLayout!AE11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF11" s="4">
+        <f>IF(PlanLayout!AF11="","",PlanLayout!AF11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG11" s="4">
+        <f>IF(PlanLayout!AG11="","",PlanLayout!AG11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH11" s="4">
+        <f>IF(PlanLayout!AH11="","",PlanLayout!AH11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI11" s="4">
+        <f>IF(PlanLayout!AI11="","",PlanLayout!AI11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="4">
+        <f>IF(PlanLayout!AJ11="","",PlanLayout!AJ11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK11" s="4">
+        <f>IF(PlanLayout!AK11="","",PlanLayout!AK11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL11" s="4">
+        <f>IF(PlanLayout!AL11="","",PlanLayout!AL11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM11" s="4">
+        <f>IF(PlanLayout!AM11="","",PlanLayout!AM11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN11" s="4">
+        <f>IF(PlanLayout!AN11="","",PlanLayout!AN11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO11" s="4">
+        <f>IF(PlanLayout!AO11="","",PlanLayout!AO11&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO11,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO11,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO11,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO11,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="B12" s="4">
+        <f>IF(PlanLayout!B12="","",PlanLayout!B12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IF(PlanLayout!C12="","",PlanLayout!C12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IF(PlanLayout!D12="","",PlanLayout!D12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IF(PlanLayout!E12="","",PlanLayout!E12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F12" s="4">
+        <f>IF(PlanLayout!F12="","",PlanLayout!F12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G12" s="4">
+        <f>IF(PlanLayout!G12="","",PlanLayout!G12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H12" s="4">
+        <f>IF(PlanLayout!H12="","",PlanLayout!H12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I12" s="4">
+        <f>IF(PlanLayout!I12="","",PlanLayout!I12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J12" s="4">
+        <f>IF(PlanLayout!J12="","",PlanLayout!J12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K12" s="4">
+        <f>IF(PlanLayout!K12="","",PlanLayout!K12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L12" s="4">
+        <f>IF(PlanLayout!L12="","",PlanLayout!L12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M12" s="4">
+        <f>IF(PlanLayout!M12="","",PlanLayout!M12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N12" s="4">
+        <f>IF(PlanLayout!N12="","",PlanLayout!N12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O12" s="4">
+        <f>IF(PlanLayout!O12="","",PlanLayout!O12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P12" s="4">
+        <f>IF(PlanLayout!P12="","",PlanLayout!P12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="4">
+        <f>IF(PlanLayout!Q12="","",PlanLayout!Q12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R12" s="4">
+        <f>IF(PlanLayout!R12="","",PlanLayout!R12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S12" s="4">
+        <f>IF(PlanLayout!S12="","",PlanLayout!S12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T12" s="4">
+        <f>IF(PlanLayout!T12="","",PlanLayout!T12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U12" s="4">
+        <f>IF(PlanLayout!U12="","",PlanLayout!U12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V12" s="4">
+        <f>IF(PlanLayout!V12="","",PlanLayout!V12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W12" s="4">
+        <f>IF(PlanLayout!W12="","",PlanLayout!W12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X12" s="4">
+        <f>IF(PlanLayout!X12="","",PlanLayout!X12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y12" s="4">
+        <f>IF(PlanLayout!Y12="","",PlanLayout!Y12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z12" s="4">
+        <f>IF(PlanLayout!Z12="","",PlanLayout!Z12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA12" s="4">
+        <f>IF(PlanLayout!AA12="","",PlanLayout!AA12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB12" s="4">
+        <f>IF(PlanLayout!AB12="","",PlanLayout!AB12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC12" s="4">
+        <f>IF(PlanLayout!AC12="","",PlanLayout!AC12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD12" s="4">
+        <f>IF(PlanLayout!AD12="","",PlanLayout!AD12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE12" s="4">
+        <f>IF(PlanLayout!AE12="","",PlanLayout!AE12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF12" s="4">
+        <f>IF(PlanLayout!AF12="","",PlanLayout!AF12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG12" s="4">
+        <f>IF(PlanLayout!AG12="","",PlanLayout!AG12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH12" s="4">
+        <f>IF(PlanLayout!AH12="","",PlanLayout!AH12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI12" s="4">
+        <f>IF(PlanLayout!AI12="","",PlanLayout!AI12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="4">
+        <f>IF(PlanLayout!AJ12="","",PlanLayout!AJ12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK12" s="4">
+        <f>IF(PlanLayout!AK12="","",PlanLayout!AK12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL12" s="4">
+        <f>IF(PlanLayout!AL12="","",PlanLayout!AL12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM12" s="4">
+        <f>IF(PlanLayout!AM12="","",PlanLayout!AM12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN12" s="4">
+        <f>IF(PlanLayout!AN12="","",PlanLayout!AN12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO12" s="4">
+        <f>IF(PlanLayout!AO12="","",PlanLayout!AO12&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO12,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO12,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO12,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO12,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="B13" s="4">
+        <f>IF(PlanLayout!B13="","",PlanLayout!B13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C13" s="4">
+        <f>IF(PlanLayout!C13="","",PlanLayout!C13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D13" s="4">
+        <f>IF(PlanLayout!D13="","",PlanLayout!D13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E13" s="4">
+        <f>IF(PlanLayout!E13="","",PlanLayout!E13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F13" s="4">
+        <f>IF(PlanLayout!F13="","",PlanLayout!F13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="4">
+        <f>IF(PlanLayout!G13="","",PlanLayout!G13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H13" s="4">
+        <f>IF(PlanLayout!H13="","",PlanLayout!H13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I13" s="4">
+        <f>IF(PlanLayout!I13="","",PlanLayout!I13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J13" s="4">
+        <f>IF(PlanLayout!J13="","",PlanLayout!J13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K13" s="4">
+        <f>IF(PlanLayout!K13="","",PlanLayout!K13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L13" s="4">
+        <f>IF(PlanLayout!L13="","",PlanLayout!L13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M13" s="4">
+        <f>IF(PlanLayout!M13="","",PlanLayout!M13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N13" s="4">
+        <f>IF(PlanLayout!N13="","",PlanLayout!N13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O13" s="4">
+        <f>IF(PlanLayout!O13="","",PlanLayout!O13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P13" s="4">
+        <f>IF(PlanLayout!P13="","",PlanLayout!P13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="4">
+        <f>IF(PlanLayout!Q13="","",PlanLayout!Q13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R13" s="4">
+        <f>IF(PlanLayout!R13="","",PlanLayout!R13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S13" s="4">
+        <f>IF(PlanLayout!S13="","",PlanLayout!S13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T13" s="4">
+        <f>IF(PlanLayout!T13="","",PlanLayout!T13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U13" s="4">
+        <f>IF(PlanLayout!U13="","",PlanLayout!U13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V13" s="4">
+        <f>IF(PlanLayout!V13="","",PlanLayout!V13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W13" s="4">
+        <f>IF(PlanLayout!W13="","",PlanLayout!W13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X13" s="4">
+        <f>IF(PlanLayout!X13="","",PlanLayout!X13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y13" s="4">
+        <f>IF(PlanLayout!Y13="","",PlanLayout!Y13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z13" s="4">
+        <f>IF(PlanLayout!Z13="","",PlanLayout!Z13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA13" s="4">
+        <f>IF(PlanLayout!AA13="","",PlanLayout!AA13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB13" s="4">
+        <f>IF(PlanLayout!AB13="","",PlanLayout!AB13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC13" s="4">
+        <f>IF(PlanLayout!AC13="","",PlanLayout!AC13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD13" s="4">
+        <f>IF(PlanLayout!AD13="","",PlanLayout!AD13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE13" s="4">
+        <f>IF(PlanLayout!AE13="","",PlanLayout!AE13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF13" s="4">
+        <f>IF(PlanLayout!AF13="","",PlanLayout!AF13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG13" s="4">
+        <f>IF(PlanLayout!AG13="","",PlanLayout!AG13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH13" s="4">
+        <f>IF(PlanLayout!AH13="","",PlanLayout!AH13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI13" s="4">
+        <f>IF(PlanLayout!AI13="","",PlanLayout!AI13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="4">
+        <f>IF(PlanLayout!AJ13="","",PlanLayout!AJ13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK13" s="4">
+        <f>IF(PlanLayout!AK13="","",PlanLayout!AK13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL13" s="4">
+        <f>IF(PlanLayout!AL13="","",PlanLayout!AL13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM13" s="4">
+        <f>IF(PlanLayout!AM13="","",PlanLayout!AM13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN13" s="4">
+        <f>IF(PlanLayout!AN13="","",PlanLayout!AN13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO13" s="4">
+        <f>IF(PlanLayout!AO13="","",PlanLayout!AO13&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO13,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO13,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO13,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO13,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="B14" s="4">
+        <f>IF(PlanLayout!B14="","",PlanLayout!B14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C14" s="4">
+        <f>IF(PlanLayout!C14="","",PlanLayout!C14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D14" s="4">
+        <f>IF(PlanLayout!D14="","",PlanLayout!D14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E14" s="4">
+        <f>IF(PlanLayout!E14="","",PlanLayout!E14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F14" s="4">
+        <f>IF(PlanLayout!F14="","",PlanLayout!F14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G14" s="4">
+        <f>IF(PlanLayout!G14="","",PlanLayout!G14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H14" s="4">
+        <f>IF(PlanLayout!H14="","",PlanLayout!H14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I14" s="4">
+        <f>IF(PlanLayout!I14="","",PlanLayout!I14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J14" s="4">
+        <f>IF(PlanLayout!J14="","",PlanLayout!J14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K14" s="4">
+        <f>IF(PlanLayout!K14="","",PlanLayout!K14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L14" s="4">
+        <f>IF(PlanLayout!L14="","",PlanLayout!L14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M14" s="4">
+        <f>IF(PlanLayout!M14="","",PlanLayout!M14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N14" s="4">
+        <f>IF(PlanLayout!N14="","",PlanLayout!N14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O14" s="4">
+        <f>IF(PlanLayout!O14="","",PlanLayout!O14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P14" s="4">
+        <f>IF(PlanLayout!P14="","",PlanLayout!P14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q14" s="4">
+        <f>IF(PlanLayout!Q14="","",PlanLayout!Q14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R14" s="4">
+        <f>IF(PlanLayout!R14="","",PlanLayout!R14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S14" s="4">
+        <f>IF(PlanLayout!S14="","",PlanLayout!S14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T14" s="4">
+        <f>IF(PlanLayout!T14="","",PlanLayout!T14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U14" s="4">
+        <f>IF(PlanLayout!U14="","",PlanLayout!U14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V14" s="4">
+        <f>IF(PlanLayout!V14="","",PlanLayout!V14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W14" s="4">
+        <f>IF(PlanLayout!W14="","",PlanLayout!W14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X14" s="4">
+        <f>IF(PlanLayout!X14="","",PlanLayout!X14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y14" s="4">
+        <f>IF(PlanLayout!Y14="","",PlanLayout!Y14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z14" s="4">
+        <f>IF(PlanLayout!Z14="","",PlanLayout!Z14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA14" s="4">
+        <f>IF(PlanLayout!AA14="","",PlanLayout!AA14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB14" s="4">
+        <f>IF(PlanLayout!AB14="","",PlanLayout!AB14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC14" s="4">
+        <f>IF(PlanLayout!AC14="","",PlanLayout!AC14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD14" s="4">
+        <f>IF(PlanLayout!AD14="","",PlanLayout!AD14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE14" s="4">
+        <f>IF(PlanLayout!AE14="","",PlanLayout!AE14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF14" s="4">
+        <f>IF(PlanLayout!AF14="","",PlanLayout!AF14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG14" s="4">
+        <f>IF(PlanLayout!AG14="","",PlanLayout!AG14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH14" s="4">
+        <f>IF(PlanLayout!AH14="","",PlanLayout!AH14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI14" s="4">
+        <f>IF(PlanLayout!AI14="","",PlanLayout!AI14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="4">
+        <f>IF(PlanLayout!AJ14="","",PlanLayout!AJ14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK14" s="4">
+        <f>IF(PlanLayout!AK14="","",PlanLayout!AK14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL14" s="4">
+        <f>IF(PlanLayout!AL14="","",PlanLayout!AL14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM14" s="4">
+        <f>IF(PlanLayout!AM14="","",PlanLayout!AM14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN14" s="4">
+        <f>IF(PlanLayout!AN14="","",PlanLayout!AN14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO14" s="4">
+        <f>IF(PlanLayout!AO14="","",PlanLayout!AO14&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO14,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO14,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO14,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO14,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="4">
+        <f>IF(PlanLayout!B15="","",PlanLayout!B15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C15" s="4">
+        <f>IF(PlanLayout!C15="","",PlanLayout!C15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D15" s="4">
+        <f>IF(PlanLayout!D15="","",PlanLayout!D15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E15" s="4">
+        <f>IF(PlanLayout!E15="","",PlanLayout!E15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F15" s="4">
+        <f>IF(PlanLayout!F15="","",PlanLayout!F15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="4">
+        <f>IF(PlanLayout!G15="","",PlanLayout!G15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H15" s="4">
+        <f>IF(PlanLayout!H15="","",PlanLayout!H15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I15" s="4">
+        <f>IF(PlanLayout!I15="","",PlanLayout!I15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J15" s="4">
+        <f>IF(PlanLayout!J15="","",PlanLayout!J15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K15" s="4">
+        <f>IF(PlanLayout!K15="","",PlanLayout!K15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L15" s="4">
+        <f>IF(PlanLayout!L15="","",PlanLayout!L15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M15" s="4">
+        <f>IF(PlanLayout!M15="","",PlanLayout!M15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N15" s="4">
+        <f>IF(PlanLayout!N15="","",PlanLayout!N15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O15" s="4">
+        <f>IF(PlanLayout!O15="","",PlanLayout!O15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P15" s="4">
+        <f>IF(PlanLayout!P15="","",PlanLayout!P15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="4">
+        <f>IF(PlanLayout!Q15="","",PlanLayout!Q15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R15" s="4">
+        <f>IF(PlanLayout!R15="","",PlanLayout!R15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S15" s="4">
+        <f>IF(PlanLayout!S15="","",PlanLayout!S15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T15" s="4">
+        <f>IF(PlanLayout!T15="","",PlanLayout!T15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U15" s="4">
+        <f>IF(PlanLayout!U15="","",PlanLayout!U15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V15" s="4">
+        <f>IF(PlanLayout!V15="","",PlanLayout!V15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W15" s="4">
+        <f>IF(PlanLayout!W15="","",PlanLayout!W15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X15" s="4">
+        <f>IF(PlanLayout!X15="","",PlanLayout!X15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y15" s="4">
+        <f>IF(PlanLayout!Y15="","",PlanLayout!Y15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z15" s="4">
+        <f>IF(PlanLayout!Z15="","",PlanLayout!Z15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA15" s="4">
+        <f>IF(PlanLayout!AA15="","",PlanLayout!AA15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB15" s="4">
+        <f>IF(PlanLayout!AB15="","",PlanLayout!AB15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC15" s="4">
+        <f>IF(PlanLayout!AC15="","",PlanLayout!AC15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD15" s="4">
+        <f>IF(PlanLayout!AD15="","",PlanLayout!AD15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE15" s="4">
+        <f>IF(PlanLayout!AE15="","",PlanLayout!AE15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF15" s="4">
+        <f>IF(PlanLayout!AF15="","",PlanLayout!AF15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG15" s="4">
+        <f>IF(PlanLayout!AG15="","",PlanLayout!AG15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH15" s="4">
+        <f>IF(PlanLayout!AH15="","",PlanLayout!AH15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI15" s="4">
+        <f>IF(PlanLayout!AI15="","",PlanLayout!AI15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="4">
+        <f>IF(PlanLayout!AJ15="","",PlanLayout!AJ15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK15" s="4">
+        <f>IF(PlanLayout!AK15="","",PlanLayout!AK15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL15" s="4">
+        <f>IF(PlanLayout!AL15="","",PlanLayout!AL15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM15" s="4">
+        <f>IF(PlanLayout!AM15="","",PlanLayout!AM15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN15" s="4">
+        <f>IF(PlanLayout!AN15="","",PlanLayout!AN15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO15" s="4">
+        <f>IF(PlanLayout!AO15="","",PlanLayout!AO15&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO15,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO15,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO15,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO15,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="4">
+        <f>IF(PlanLayout!B16="","",PlanLayout!B16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C16" s="4">
+        <f>IF(PlanLayout!C16="","",PlanLayout!C16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IF(PlanLayout!D16="","",PlanLayout!D16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IF(PlanLayout!E16="","",PlanLayout!E16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F16" s="4">
+        <f>IF(PlanLayout!F16="","",PlanLayout!F16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G16" s="4">
+        <f>IF(PlanLayout!G16="","",PlanLayout!G16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H16" s="4">
+        <f>IF(PlanLayout!H16="","",PlanLayout!H16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I16" s="4">
+        <f>IF(PlanLayout!I16="","",PlanLayout!I16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J16" s="4">
+        <f>IF(PlanLayout!J16="","",PlanLayout!J16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K16" s="4">
+        <f>IF(PlanLayout!K16="","",PlanLayout!K16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L16" s="4">
+        <f>IF(PlanLayout!L16="","",PlanLayout!L16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M16" s="4">
+        <f>IF(PlanLayout!M16="","",PlanLayout!M16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N16" s="4">
+        <f>IF(PlanLayout!N16="","",PlanLayout!N16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O16" s="4">
+        <f>IF(PlanLayout!O16="","",PlanLayout!O16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P16" s="4">
+        <f>IF(PlanLayout!P16="","",PlanLayout!P16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q16" s="4">
+        <f>IF(PlanLayout!Q16="","",PlanLayout!Q16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R16" s="4">
+        <f>IF(PlanLayout!R16="","",PlanLayout!R16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S16" s="4">
+        <f>IF(PlanLayout!S16="","",PlanLayout!S16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T16" s="4">
+        <f>IF(PlanLayout!T16="","",PlanLayout!T16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U16" s="4">
+        <f>IF(PlanLayout!U16="","",PlanLayout!U16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V16" s="4">
+        <f>IF(PlanLayout!V16="","",PlanLayout!V16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W16" s="4">
+        <f>IF(PlanLayout!W16="","",PlanLayout!W16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X16" s="4">
+        <f>IF(PlanLayout!X16="","",PlanLayout!X16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y16" s="4">
+        <f>IF(PlanLayout!Y16="","",PlanLayout!Y16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z16" s="4">
+        <f>IF(PlanLayout!Z16="","",PlanLayout!Z16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA16" s="4">
+        <f>IF(PlanLayout!AA16="","",PlanLayout!AA16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB16" s="4">
+        <f>IF(PlanLayout!AB16="","",PlanLayout!AB16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC16" s="4">
+        <f>IF(PlanLayout!AC16="","",PlanLayout!AC16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD16" s="4">
+        <f>IF(PlanLayout!AD16="","",PlanLayout!AD16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="4">
+        <f>IF(PlanLayout!AE16="","",PlanLayout!AE16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF16" s="4">
+        <f>IF(PlanLayout!AF16="","",PlanLayout!AF16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG16" s="4">
+        <f>IF(PlanLayout!AG16="","",PlanLayout!AG16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH16" s="4">
+        <f>IF(PlanLayout!AH16="","",PlanLayout!AH16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI16" s="4">
+        <f>IF(PlanLayout!AI16="","",PlanLayout!AI16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="4">
+        <f>IF(PlanLayout!AJ16="","",PlanLayout!AJ16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK16" s="4">
+        <f>IF(PlanLayout!AK16="","",PlanLayout!AK16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL16" s="4">
+        <f>IF(PlanLayout!AL16="","",PlanLayout!AL16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM16" s="4">
+        <f>IF(PlanLayout!AM16="","",PlanLayout!AM16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN16" s="4">
+        <f>IF(PlanLayout!AN16="","",PlanLayout!AN16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO16" s="4">
+        <f>IF(PlanLayout!AO16="","",PlanLayout!AO16&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO16,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO16,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO16,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO16,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="B17" s="4">
+        <f>IF(PlanLayout!B17="","",PlanLayout!B17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C17" s="4">
+        <f>IF(PlanLayout!C17="","",PlanLayout!C17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D17" s="4">
+        <f>IF(PlanLayout!D17="","",PlanLayout!D17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E17" s="4">
+        <f>IF(PlanLayout!E17="","",PlanLayout!E17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F17" s="4">
+        <f>IF(PlanLayout!F17="","",PlanLayout!F17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G17" s="4">
+        <f>IF(PlanLayout!G17="","",PlanLayout!G17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H17" s="4">
+        <f>IF(PlanLayout!H17="","",PlanLayout!H17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I17" s="4">
+        <f>IF(PlanLayout!I17="","",PlanLayout!I17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J17" s="4">
+        <f>IF(PlanLayout!J17="","",PlanLayout!J17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K17" s="4">
+        <f>IF(PlanLayout!K17="","",PlanLayout!K17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L17" s="4">
+        <f>IF(PlanLayout!L17="","",PlanLayout!L17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M17" s="4">
+        <f>IF(PlanLayout!M17="","",PlanLayout!M17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N17" s="4">
+        <f>IF(PlanLayout!N17="","",PlanLayout!N17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O17" s="4">
+        <f>IF(PlanLayout!O17="","",PlanLayout!O17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P17" s="4">
+        <f>IF(PlanLayout!P17="","",PlanLayout!P17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q17" s="4">
+        <f>IF(PlanLayout!Q17="","",PlanLayout!Q17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R17" s="4">
+        <f>IF(PlanLayout!R17="","",PlanLayout!R17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S17" s="4">
+        <f>IF(PlanLayout!S17="","",PlanLayout!S17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T17" s="4">
+        <f>IF(PlanLayout!T17="","",PlanLayout!T17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U17" s="4">
+        <f>IF(PlanLayout!U17="","",PlanLayout!U17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V17" s="4">
+        <f>IF(PlanLayout!V17="","",PlanLayout!V17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W17" s="4">
+        <f>IF(PlanLayout!W17="","",PlanLayout!W17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X17" s="4">
+        <f>IF(PlanLayout!X17="","",PlanLayout!X17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y17" s="4">
+        <f>IF(PlanLayout!Y17="","",PlanLayout!Y17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z17" s="4">
+        <f>IF(PlanLayout!Z17="","",PlanLayout!Z17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA17" s="4">
+        <f>IF(PlanLayout!AA17="","",PlanLayout!AA17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB17" s="4">
+        <f>IF(PlanLayout!AB17="","",PlanLayout!AB17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC17" s="4">
+        <f>IF(PlanLayout!AC17="","",PlanLayout!AC17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD17" s="4">
+        <f>IF(PlanLayout!AD17="","",PlanLayout!AD17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="4">
+        <f>IF(PlanLayout!AE17="","",PlanLayout!AE17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF17" s="4">
+        <f>IF(PlanLayout!AF17="","",PlanLayout!AF17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG17" s="4">
+        <f>IF(PlanLayout!AG17="","",PlanLayout!AG17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH17" s="4">
+        <f>IF(PlanLayout!AH17="","",PlanLayout!AH17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI17" s="4">
+        <f>IF(PlanLayout!AI17="","",PlanLayout!AI17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="4">
+        <f>IF(PlanLayout!AJ17="","",PlanLayout!AJ17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK17" s="4">
+        <f>IF(PlanLayout!AK17="","",PlanLayout!AK17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL17" s="4">
+        <f>IF(PlanLayout!AL17="","",PlanLayout!AL17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM17" s="4">
+        <f>IF(PlanLayout!AM17="","",PlanLayout!AM17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN17" s="4">
+        <f>IF(PlanLayout!AN17="","",PlanLayout!AN17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO17" s="4">
+        <f>IF(PlanLayout!AO17="","",PlanLayout!AO17&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO17,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO17,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO17,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO17,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="B18" s="4">
+        <f>IF(PlanLayout!B18="","",PlanLayout!B18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C18" s="4">
+        <f>IF(PlanLayout!C18="","",PlanLayout!C18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D18" s="4">
+        <f>IF(PlanLayout!D18="","",PlanLayout!D18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E18" s="4">
+        <f>IF(PlanLayout!E18="","",PlanLayout!E18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F18" s="4">
+        <f>IF(PlanLayout!F18="","",PlanLayout!F18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G18" s="4">
+        <f>IF(PlanLayout!G18="","",PlanLayout!G18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H18" s="4">
+        <f>IF(PlanLayout!H18="","",PlanLayout!H18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I18" s="4">
+        <f>IF(PlanLayout!I18="","",PlanLayout!I18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J18" s="4">
+        <f>IF(PlanLayout!J18="","",PlanLayout!J18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K18" s="4">
+        <f>IF(PlanLayout!K18="","",PlanLayout!K18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L18" s="4">
+        <f>IF(PlanLayout!L18="","",PlanLayout!L18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M18" s="4">
+        <f>IF(PlanLayout!M18="","",PlanLayout!M18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N18" s="4">
+        <f>IF(PlanLayout!N18="","",PlanLayout!N18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O18" s="4">
+        <f>IF(PlanLayout!O18="","",PlanLayout!O18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P18" s="4">
+        <f>IF(PlanLayout!P18="","",PlanLayout!P18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q18" s="4">
+        <f>IF(PlanLayout!Q18="","",PlanLayout!Q18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R18" s="4">
+        <f>IF(PlanLayout!R18="","",PlanLayout!R18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S18" s="4">
+        <f>IF(PlanLayout!S18="","",PlanLayout!S18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T18" s="4">
+        <f>IF(PlanLayout!T18="","",PlanLayout!T18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U18" s="4">
+        <f>IF(PlanLayout!U18="","",PlanLayout!U18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V18" s="4">
+        <f>IF(PlanLayout!V18="","",PlanLayout!V18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W18" s="4">
+        <f>IF(PlanLayout!W18="","",PlanLayout!W18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X18" s="4">
+        <f>IF(PlanLayout!X18="","",PlanLayout!X18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y18" s="4">
+        <f>IF(PlanLayout!Y18="","",PlanLayout!Y18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z18" s="4">
+        <f>IF(PlanLayout!Z18="","",PlanLayout!Z18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA18" s="4">
+        <f>IF(PlanLayout!AA18="","",PlanLayout!AA18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB18" s="4">
+        <f>IF(PlanLayout!AB18="","",PlanLayout!AB18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC18" s="4">
+        <f>IF(PlanLayout!AC18="","",PlanLayout!AC18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD18" s="4">
+        <f>IF(PlanLayout!AD18="","",PlanLayout!AD18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="4">
+        <f>IF(PlanLayout!AE18="","",PlanLayout!AE18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF18" s="4">
+        <f>IF(PlanLayout!AF18="","",PlanLayout!AF18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG18" s="4">
+        <f>IF(PlanLayout!AG18="","",PlanLayout!AG18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH18" s="4">
+        <f>IF(PlanLayout!AH18="","",PlanLayout!AH18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI18" s="4">
+        <f>IF(PlanLayout!AI18="","",PlanLayout!AI18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="4">
+        <f>IF(PlanLayout!AJ18="","",PlanLayout!AJ18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK18" s="4">
+        <f>IF(PlanLayout!AK18="","",PlanLayout!AK18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL18" s="4">
+        <f>IF(PlanLayout!AL18="","",PlanLayout!AL18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM18" s="4">
+        <f>IF(PlanLayout!AM18="","",PlanLayout!AM18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN18" s="4">
+        <f>IF(PlanLayout!AN18="","",PlanLayout!AN18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO18" s="4">
+        <f>IF(PlanLayout!AO18="","",PlanLayout!AO18&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO18,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO18,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO18,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO18,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="4">
+        <f>IF(PlanLayout!B19="","",PlanLayout!B19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C19" s="4">
+        <f>IF(PlanLayout!C19="","",PlanLayout!C19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D19" s="4">
+        <f>IF(PlanLayout!D19="","",PlanLayout!D19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E19" s="4">
+        <f>IF(PlanLayout!E19="","",PlanLayout!E19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F19" s="4">
+        <f>IF(PlanLayout!F19="","",PlanLayout!F19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G19" s="4">
+        <f>IF(PlanLayout!G19="","",PlanLayout!G19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H19" s="4">
+        <f>IF(PlanLayout!H19="","",PlanLayout!H19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I19" s="4">
+        <f>IF(PlanLayout!I19="","",PlanLayout!I19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J19" s="4">
+        <f>IF(PlanLayout!J19="","",PlanLayout!J19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K19" s="4">
+        <f>IF(PlanLayout!K19="","",PlanLayout!K19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L19" s="4">
+        <f>IF(PlanLayout!L19="","",PlanLayout!L19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M19" s="4">
+        <f>IF(PlanLayout!M19="","",PlanLayout!M19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N19" s="4">
+        <f>IF(PlanLayout!N19="","",PlanLayout!N19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O19" s="4">
+        <f>IF(PlanLayout!O19="","",PlanLayout!O19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P19" s="4">
+        <f>IF(PlanLayout!P19="","",PlanLayout!P19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q19" s="4">
+        <f>IF(PlanLayout!Q19="","",PlanLayout!Q19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R19" s="4">
+        <f>IF(PlanLayout!R19="","",PlanLayout!R19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S19" s="4">
+        <f>IF(PlanLayout!S19="","",PlanLayout!S19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T19" s="4">
+        <f>IF(PlanLayout!T19="","",PlanLayout!T19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U19" s="4">
+        <f>IF(PlanLayout!U19="","",PlanLayout!U19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V19" s="4">
+        <f>IF(PlanLayout!V19="","",PlanLayout!V19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W19" s="4">
+        <f>IF(PlanLayout!W19="","",PlanLayout!W19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X19" s="4">
+        <f>IF(PlanLayout!X19="","",PlanLayout!X19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y19" s="4">
+        <f>IF(PlanLayout!Y19="","",PlanLayout!Y19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z19" s="4">
+        <f>IF(PlanLayout!Z19="","",PlanLayout!Z19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA19" s="4">
+        <f>IF(PlanLayout!AA19="","",PlanLayout!AA19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB19" s="4">
+        <f>IF(PlanLayout!AB19="","",PlanLayout!AB19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC19" s="4">
+        <f>IF(PlanLayout!AC19="","",PlanLayout!AC19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD19" s="4">
+        <f>IF(PlanLayout!AD19="","",PlanLayout!AD19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE19" s="4">
+        <f>IF(PlanLayout!AE19="","",PlanLayout!AE19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF19" s="4">
+        <f>IF(PlanLayout!AF19="","",PlanLayout!AF19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG19" s="4">
+        <f>IF(PlanLayout!AG19="","",PlanLayout!AG19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH19" s="4">
+        <f>IF(PlanLayout!AH19="","",PlanLayout!AH19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI19" s="4">
+        <f>IF(PlanLayout!AI19="","",PlanLayout!AI19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="4">
+        <f>IF(PlanLayout!AJ19="","",PlanLayout!AJ19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK19" s="4">
+        <f>IF(PlanLayout!AK19="","",PlanLayout!AK19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL19" s="4">
+        <f>IF(PlanLayout!AL19="","",PlanLayout!AL19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM19" s="4">
+        <f>IF(PlanLayout!AM19="","",PlanLayout!AM19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN19" s="4">
+        <f>IF(PlanLayout!AN19="","",PlanLayout!AN19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO19" s="4">
+        <f>IF(PlanLayout!AO19="","",PlanLayout!AO19&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO19,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO19,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO19,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO19,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="4">
+        <f>IF(PlanLayout!B20="","",PlanLayout!B20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C20" s="4">
+        <f>IF(PlanLayout!C20="","",PlanLayout!C20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D20" s="4">
+        <f>IF(PlanLayout!D20="","",PlanLayout!D20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E20" s="4">
+        <f>IF(PlanLayout!E20="","",PlanLayout!E20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F20" s="4">
+        <f>IF(PlanLayout!F20="","",PlanLayout!F20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G20" s="4">
+        <f>IF(PlanLayout!G20="","",PlanLayout!G20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H20" s="4">
+        <f>IF(PlanLayout!H20="","",PlanLayout!H20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I20" s="4">
+        <f>IF(PlanLayout!I20="","",PlanLayout!I20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J20" s="4">
+        <f>IF(PlanLayout!J20="","",PlanLayout!J20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K20" s="4">
+        <f>IF(PlanLayout!K20="","",PlanLayout!K20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L20" s="4">
+        <f>IF(PlanLayout!L20="","",PlanLayout!L20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M20" s="4">
+        <f>IF(PlanLayout!M20="","",PlanLayout!M20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N20" s="4">
+        <f>IF(PlanLayout!N20="","",PlanLayout!N20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O20" s="4">
+        <f>IF(PlanLayout!O20="","",PlanLayout!O20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P20" s="4">
+        <f>IF(PlanLayout!P20="","",PlanLayout!P20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q20" s="4">
+        <f>IF(PlanLayout!Q20="","",PlanLayout!Q20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R20" s="4">
+        <f>IF(PlanLayout!R20="","",PlanLayout!R20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S20" s="4">
+        <f>IF(PlanLayout!S20="","",PlanLayout!S20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T20" s="4">
+        <f>IF(PlanLayout!T20="","",PlanLayout!T20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U20" s="4">
+        <f>IF(PlanLayout!U20="","",PlanLayout!U20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V20" s="4">
+        <f>IF(PlanLayout!V20="","",PlanLayout!V20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W20" s="4">
+        <f>IF(PlanLayout!W20="","",PlanLayout!W20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X20" s="4">
+        <f>IF(PlanLayout!X20="","",PlanLayout!X20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y20" s="4">
+        <f>IF(PlanLayout!Y20="","",PlanLayout!Y20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z20" s="4">
+        <f>IF(PlanLayout!Z20="","",PlanLayout!Z20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA20" s="4">
+        <f>IF(PlanLayout!AA20="","",PlanLayout!AA20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB20" s="4">
+        <f>IF(PlanLayout!AB20="","",PlanLayout!AB20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC20" s="4">
+        <f>IF(PlanLayout!AC20="","",PlanLayout!AC20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD20" s="4">
+        <f>IF(PlanLayout!AD20="","",PlanLayout!AD20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE20" s="4">
+        <f>IF(PlanLayout!AE20="","",PlanLayout!AE20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF20" s="4">
+        <f>IF(PlanLayout!AF20="","",PlanLayout!AF20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG20" s="4">
+        <f>IF(PlanLayout!AG20="","",PlanLayout!AG20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH20" s="4">
+        <f>IF(PlanLayout!AH20="","",PlanLayout!AH20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI20" s="4">
+        <f>IF(PlanLayout!AI20="","",PlanLayout!AI20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="4">
+        <f>IF(PlanLayout!AJ20="","",PlanLayout!AJ20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK20" s="4">
+        <f>IF(PlanLayout!AK20="","",PlanLayout!AK20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL20" s="4">
+        <f>IF(PlanLayout!AL20="","",PlanLayout!AL20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM20" s="4">
+        <f>IF(PlanLayout!AM20="","",PlanLayout!AM20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN20" s="4">
+        <f>IF(PlanLayout!AN20="","",PlanLayout!AN20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO20" s="4">
+        <f>IF(PlanLayout!AO20="","",PlanLayout!AO20&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO20,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO20,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO20,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO20,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="4">
+        <f>IF(PlanLayout!B21="","",PlanLayout!B21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C21" s="4">
+        <f>IF(PlanLayout!C21="","",PlanLayout!C21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D21" s="4">
+        <f>IF(PlanLayout!D21="","",PlanLayout!D21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E21" s="4">
+        <f>IF(PlanLayout!E21="","",PlanLayout!E21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F21" s="4">
+        <f>IF(PlanLayout!F21="","",PlanLayout!F21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G21" s="4">
+        <f>IF(PlanLayout!G21="","",PlanLayout!G21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H21" s="4">
+        <f>IF(PlanLayout!H21="","",PlanLayout!H21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I21" s="4">
+        <f>IF(PlanLayout!I21="","",PlanLayout!I21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J21" s="4">
+        <f>IF(PlanLayout!J21="","",PlanLayout!J21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K21" s="4">
+        <f>IF(PlanLayout!K21="","",PlanLayout!K21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L21" s="4">
+        <f>IF(PlanLayout!L21="","",PlanLayout!L21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M21" s="4">
+        <f>IF(PlanLayout!M21="","",PlanLayout!M21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N21" s="4">
+        <f>IF(PlanLayout!N21="","",PlanLayout!N21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O21" s="4">
+        <f>IF(PlanLayout!O21="","",PlanLayout!O21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P21" s="4">
+        <f>IF(PlanLayout!P21="","",PlanLayout!P21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q21" s="4">
+        <f>IF(PlanLayout!Q21="","",PlanLayout!Q21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R21" s="4">
+        <f>IF(PlanLayout!R21="","",PlanLayout!R21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S21" s="4">
+        <f>IF(PlanLayout!S21="","",PlanLayout!S21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T21" s="4">
+        <f>IF(PlanLayout!T21="","",PlanLayout!T21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U21" s="4">
+        <f>IF(PlanLayout!U21="","",PlanLayout!U21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V21" s="4">
+        <f>IF(PlanLayout!V21="","",PlanLayout!V21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W21" s="4">
+        <f>IF(PlanLayout!W21="","",PlanLayout!W21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X21" s="4">
+        <f>IF(PlanLayout!X21="","",PlanLayout!X21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y21" s="4">
+        <f>IF(PlanLayout!Y21="","",PlanLayout!Y21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z21" s="4">
+        <f>IF(PlanLayout!Z21="","",PlanLayout!Z21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA21" s="4">
+        <f>IF(PlanLayout!AA21="","",PlanLayout!AA21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB21" s="4">
+        <f>IF(PlanLayout!AB21="","",PlanLayout!AB21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC21" s="4">
+        <f>IF(PlanLayout!AC21="","",PlanLayout!AC21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD21" s="4">
+        <f>IF(PlanLayout!AD21="","",PlanLayout!AD21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE21" s="4">
+        <f>IF(PlanLayout!AE21="","",PlanLayout!AE21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF21" s="4">
+        <f>IF(PlanLayout!AF21="","",PlanLayout!AF21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG21" s="4">
+        <f>IF(PlanLayout!AG21="","",PlanLayout!AG21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH21" s="4">
+        <f>IF(PlanLayout!AH21="","",PlanLayout!AH21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI21" s="4">
+        <f>IF(PlanLayout!AI21="","",PlanLayout!AI21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="4">
+        <f>IF(PlanLayout!AJ21="","",PlanLayout!AJ21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK21" s="4">
+        <f>IF(PlanLayout!AK21="","",PlanLayout!AK21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL21" s="4">
+        <f>IF(PlanLayout!AL21="","",PlanLayout!AL21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM21" s="4">
+        <f>IF(PlanLayout!AM21="","",PlanLayout!AM21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN21" s="4">
+        <f>IF(PlanLayout!AN21="","",PlanLayout!AN21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO21" s="4">
+        <f>IF(PlanLayout!AO21="","",PlanLayout!AO21&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO21,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO21,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO21,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO21,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="B22" s="4">
+        <f>IF(PlanLayout!B22="","",PlanLayout!B22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C22" s="4">
+        <f>IF(PlanLayout!C22="","",PlanLayout!C22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D22" s="4">
+        <f>IF(PlanLayout!D22="","",PlanLayout!D22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E22" s="4">
+        <f>IF(PlanLayout!E22="","",PlanLayout!E22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F22" s="4">
+        <f>IF(PlanLayout!F22="","",PlanLayout!F22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G22" s="4">
+        <f>IF(PlanLayout!G22="","",PlanLayout!G22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H22" s="4">
+        <f>IF(PlanLayout!H22="","",PlanLayout!H22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I22" s="4">
+        <f>IF(PlanLayout!I22="","",PlanLayout!I22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J22" s="4">
+        <f>IF(PlanLayout!J22="","",PlanLayout!J22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K22" s="4">
+        <f>IF(PlanLayout!K22="","",PlanLayout!K22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L22" s="4">
+        <f>IF(PlanLayout!L22="","",PlanLayout!L22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M22" s="4">
+        <f>IF(PlanLayout!M22="","",PlanLayout!M22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N22" s="4">
+        <f>IF(PlanLayout!N22="","",PlanLayout!N22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O22" s="4">
+        <f>IF(PlanLayout!O22="","",PlanLayout!O22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P22" s="4">
+        <f>IF(PlanLayout!P22="","",PlanLayout!P22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q22" s="4">
+        <f>IF(PlanLayout!Q22="","",PlanLayout!Q22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R22" s="4">
+        <f>IF(PlanLayout!R22="","",PlanLayout!R22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S22" s="4">
+        <f>IF(PlanLayout!S22="","",PlanLayout!S22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T22" s="4">
+        <f>IF(PlanLayout!T22="","",PlanLayout!T22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U22" s="4">
+        <f>IF(PlanLayout!U22="","",PlanLayout!U22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V22" s="4">
+        <f>IF(PlanLayout!V22="","",PlanLayout!V22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W22" s="4">
+        <f>IF(PlanLayout!W22="","",PlanLayout!W22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X22" s="4">
+        <f>IF(PlanLayout!X22="","",PlanLayout!X22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y22" s="4">
+        <f>IF(PlanLayout!Y22="","",PlanLayout!Y22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z22" s="4">
+        <f>IF(PlanLayout!Z22="","",PlanLayout!Z22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA22" s="4">
+        <f>IF(PlanLayout!AA22="","",PlanLayout!AA22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB22" s="4">
+        <f>IF(PlanLayout!AB22="","",PlanLayout!AB22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC22" s="4">
+        <f>IF(PlanLayout!AC22="","",PlanLayout!AC22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD22" s="4">
+        <f>IF(PlanLayout!AD22="","",PlanLayout!AD22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE22" s="4">
+        <f>IF(PlanLayout!AE22="","",PlanLayout!AE22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF22" s="4">
+        <f>IF(PlanLayout!AF22="","",PlanLayout!AF22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG22" s="4">
+        <f>IF(PlanLayout!AG22="","",PlanLayout!AG22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH22" s="4">
+        <f>IF(PlanLayout!AH22="","",PlanLayout!AH22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI22" s="4">
+        <f>IF(PlanLayout!AI22="","",PlanLayout!AI22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ22" s="4">
+        <f>IF(PlanLayout!AJ22="","",PlanLayout!AJ22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK22" s="4">
+        <f>IF(PlanLayout!AK22="","",PlanLayout!AK22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL22" s="4">
+        <f>IF(PlanLayout!AL22="","",PlanLayout!AL22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM22" s="4">
+        <f>IF(PlanLayout!AM22="","",PlanLayout!AM22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN22" s="4">
+        <f>IF(PlanLayout!AN22="","",PlanLayout!AN22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO22" s="4">
+        <f>IF(PlanLayout!AO22="","",PlanLayout!AO22&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO22,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO22,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO22,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO22,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="4">
+        <f>IF(PlanLayout!B23="","",PlanLayout!B23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C23" s="4">
+        <f>IF(PlanLayout!C23="","",PlanLayout!C23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D23" s="4">
+        <f>IF(PlanLayout!D23="","",PlanLayout!D23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E23" s="4">
+        <f>IF(PlanLayout!E23="","",PlanLayout!E23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F23" s="4">
+        <f>IF(PlanLayout!F23="","",PlanLayout!F23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G23" s="4">
+        <f>IF(PlanLayout!G23="","",PlanLayout!G23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H23" s="4">
+        <f>IF(PlanLayout!H23="","",PlanLayout!H23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I23" s="4">
+        <f>IF(PlanLayout!I23="","",PlanLayout!I23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J23" s="4">
+        <f>IF(PlanLayout!J23="","",PlanLayout!J23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K23" s="4">
+        <f>IF(PlanLayout!K23="","",PlanLayout!K23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L23" s="4">
+        <f>IF(PlanLayout!L23="","",PlanLayout!L23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M23" s="4">
+        <f>IF(PlanLayout!M23="","",PlanLayout!M23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N23" s="4">
+        <f>IF(PlanLayout!N23="","",PlanLayout!N23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O23" s="4">
+        <f>IF(PlanLayout!O23="","",PlanLayout!O23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P23" s="4">
+        <f>IF(PlanLayout!P23="","",PlanLayout!P23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q23" s="4">
+        <f>IF(PlanLayout!Q23="","",PlanLayout!Q23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R23" s="4">
+        <f>IF(PlanLayout!R23="","",PlanLayout!R23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S23" s="4">
+        <f>IF(PlanLayout!S23="","",PlanLayout!S23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T23" s="4">
+        <f>IF(PlanLayout!T23="","",PlanLayout!T23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U23" s="4">
+        <f>IF(PlanLayout!U23="","",PlanLayout!U23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V23" s="4">
+        <f>IF(PlanLayout!V23="","",PlanLayout!V23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W23" s="4">
+        <f>IF(PlanLayout!W23="","",PlanLayout!W23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X23" s="4">
+        <f>IF(PlanLayout!X23="","",PlanLayout!X23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y23" s="4">
+        <f>IF(PlanLayout!Y23="","",PlanLayout!Y23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z23" s="4">
+        <f>IF(PlanLayout!Z23="","",PlanLayout!Z23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA23" s="4">
+        <f>IF(PlanLayout!AA23="","",PlanLayout!AA23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB23" s="4">
+        <f>IF(PlanLayout!AB23="","",PlanLayout!AB23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC23" s="4">
+        <f>IF(PlanLayout!AC23="","",PlanLayout!AC23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD23" s="4">
+        <f>IF(PlanLayout!AD23="","",PlanLayout!AD23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE23" s="4">
+        <f>IF(PlanLayout!AE23="","",PlanLayout!AE23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF23" s="4">
+        <f>IF(PlanLayout!AF23="","",PlanLayout!AF23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG23" s="4">
+        <f>IF(PlanLayout!AG23="","",PlanLayout!AG23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH23" s="4">
+        <f>IF(PlanLayout!AH23="","",PlanLayout!AH23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI23" s="4">
+        <f>IF(PlanLayout!AI23="","",PlanLayout!AI23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ23" s="4">
+        <f>IF(PlanLayout!AJ23="","",PlanLayout!AJ23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK23" s="4">
+        <f>IF(PlanLayout!AK23="","",PlanLayout!AK23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL23" s="4">
+        <f>IF(PlanLayout!AL23="","",PlanLayout!AL23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM23" s="4">
+        <f>IF(PlanLayout!AM23="","",PlanLayout!AM23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN23" s="4">
+        <f>IF(PlanLayout!AN23="","",PlanLayout!AN23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO23" s="4">
+        <f>IF(PlanLayout!AO23="","",PlanLayout!AO23&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO23,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO23,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO23,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO23,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="4">
+        <f>IF(PlanLayout!B24="","",PlanLayout!B24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C24" s="4">
+        <f>IF(PlanLayout!C24="","",PlanLayout!C24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D24" s="4">
+        <f>IF(PlanLayout!D24="","",PlanLayout!D24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E24" s="4">
+        <f>IF(PlanLayout!E24="","",PlanLayout!E24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F24" s="4">
+        <f>IF(PlanLayout!F24="","",PlanLayout!F24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G24" s="4">
+        <f>IF(PlanLayout!G24="","",PlanLayout!G24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H24" s="4">
+        <f>IF(PlanLayout!H24="","",PlanLayout!H24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I24" s="4">
+        <f>IF(PlanLayout!I24="","",PlanLayout!I24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J24" s="4">
+        <f>IF(PlanLayout!J24="","",PlanLayout!J24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K24" s="4">
+        <f>IF(PlanLayout!K24="","",PlanLayout!K24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L24" s="4">
+        <f>IF(PlanLayout!L24="","",PlanLayout!L24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M24" s="4">
+        <f>IF(PlanLayout!M24="","",PlanLayout!M24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N24" s="4">
+        <f>IF(PlanLayout!N24="","",PlanLayout!N24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O24" s="4">
+        <f>IF(PlanLayout!O24="","",PlanLayout!O24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P24" s="4">
+        <f>IF(PlanLayout!P24="","",PlanLayout!P24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q24" s="4">
+        <f>IF(PlanLayout!Q24="","",PlanLayout!Q24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R24" s="4">
+        <f>IF(PlanLayout!R24="","",PlanLayout!R24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S24" s="4">
+        <f>IF(PlanLayout!S24="","",PlanLayout!S24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T24" s="4">
+        <f>IF(PlanLayout!T24="","",PlanLayout!T24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U24" s="4">
+        <f>IF(PlanLayout!U24="","",PlanLayout!U24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V24" s="4">
+        <f>IF(PlanLayout!V24="","",PlanLayout!V24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W24" s="4">
+        <f>IF(PlanLayout!W24="","",PlanLayout!W24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X24" s="4">
+        <f>IF(PlanLayout!X24="","",PlanLayout!X24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y24" s="4">
+        <f>IF(PlanLayout!Y24="","",PlanLayout!Y24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z24" s="4">
+        <f>IF(PlanLayout!Z24="","",PlanLayout!Z24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA24" s="4">
+        <f>IF(PlanLayout!AA24="","",PlanLayout!AA24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB24" s="4">
+        <f>IF(PlanLayout!AB24="","",PlanLayout!AB24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC24" s="4">
+        <f>IF(PlanLayout!AC24="","",PlanLayout!AC24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD24" s="4">
+        <f>IF(PlanLayout!AD24="","",PlanLayout!AD24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE24" s="4">
+        <f>IF(PlanLayout!AE24="","",PlanLayout!AE24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF24" s="4">
+        <f>IF(PlanLayout!AF24="","",PlanLayout!AF24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG24" s="4">
+        <f>IF(PlanLayout!AG24="","",PlanLayout!AG24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH24" s="4">
+        <f>IF(PlanLayout!AH24="","",PlanLayout!AH24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI24" s="4">
+        <f>IF(PlanLayout!AI24="","",PlanLayout!AI24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ24" s="4">
+        <f>IF(PlanLayout!AJ24="","",PlanLayout!AJ24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK24" s="4">
+        <f>IF(PlanLayout!AK24="","",PlanLayout!AK24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL24" s="4">
+        <f>IF(PlanLayout!AL24="","",PlanLayout!AL24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM24" s="4">
+        <f>IF(PlanLayout!AM24="","",PlanLayout!AM24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN24" s="4">
+        <f>IF(PlanLayout!AN24="","",PlanLayout!AN24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO24" s="4">
+        <f>IF(PlanLayout!AO24="","",PlanLayout!AO24&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO24,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO24,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO24,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO24,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="4">
+        <f>IF(PlanLayout!B25="","",PlanLayout!B25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C25" s="4">
+        <f>IF(PlanLayout!C25="","",PlanLayout!C25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D25" s="4">
+        <f>IF(PlanLayout!D25="","",PlanLayout!D25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E25" s="4">
+        <f>IF(PlanLayout!E25="","",PlanLayout!E25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F25" s="4">
+        <f>IF(PlanLayout!F25="","",PlanLayout!F25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G25" s="4">
+        <f>IF(PlanLayout!G25="","",PlanLayout!G25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H25" s="4">
+        <f>IF(PlanLayout!H25="","",PlanLayout!H25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I25" s="4">
+        <f>IF(PlanLayout!I25="","",PlanLayout!I25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J25" s="4">
+        <f>IF(PlanLayout!J25="","",PlanLayout!J25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K25" s="4">
+        <f>IF(PlanLayout!K25="","",PlanLayout!K25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L25" s="4">
+        <f>IF(PlanLayout!L25="","",PlanLayout!L25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M25" s="4">
+        <f>IF(PlanLayout!M25="","",PlanLayout!M25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N25" s="4">
+        <f>IF(PlanLayout!N25="","",PlanLayout!N25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O25" s="4">
+        <f>IF(PlanLayout!O25="","",PlanLayout!O25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P25" s="4">
+        <f>IF(PlanLayout!P25="","",PlanLayout!P25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q25" s="4">
+        <f>IF(PlanLayout!Q25="","",PlanLayout!Q25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R25" s="4">
+        <f>IF(PlanLayout!R25="","",PlanLayout!R25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S25" s="4">
+        <f>IF(PlanLayout!S25="","",PlanLayout!S25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T25" s="4">
+        <f>IF(PlanLayout!T25="","",PlanLayout!T25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U25" s="4">
+        <f>IF(PlanLayout!U25="","",PlanLayout!U25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V25" s="4">
+        <f>IF(PlanLayout!V25="","",PlanLayout!V25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W25" s="4">
+        <f>IF(PlanLayout!W25="","",PlanLayout!W25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X25" s="4">
+        <f>IF(PlanLayout!X25="","",PlanLayout!X25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y25" s="4">
+        <f>IF(PlanLayout!Y25="","",PlanLayout!Y25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z25" s="4">
+        <f>IF(PlanLayout!Z25="","",PlanLayout!Z25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA25" s="4">
+        <f>IF(PlanLayout!AA25="","",PlanLayout!AA25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB25" s="4">
+        <f>IF(PlanLayout!AB25="","",PlanLayout!AB25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC25" s="4">
+        <f>IF(PlanLayout!AC25="","",PlanLayout!AC25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD25" s="4">
+        <f>IF(PlanLayout!AD25="","",PlanLayout!AD25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE25" s="4">
+        <f>IF(PlanLayout!AE25="","",PlanLayout!AE25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF25" s="4">
+        <f>IF(PlanLayout!AF25="","",PlanLayout!AF25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG25" s="4">
+        <f>IF(PlanLayout!AG25="","",PlanLayout!AG25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH25" s="4">
+        <f>IF(PlanLayout!AH25="","",PlanLayout!AH25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI25" s="4">
+        <f>IF(PlanLayout!AI25="","",PlanLayout!AI25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ25" s="4">
+        <f>IF(PlanLayout!AJ25="","",PlanLayout!AJ25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK25" s="4">
+        <f>IF(PlanLayout!AK25="","",PlanLayout!AK25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL25" s="4">
+        <f>IF(PlanLayout!AL25="","",PlanLayout!AL25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM25" s="4">
+        <f>IF(PlanLayout!AM25="","",PlanLayout!AM25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN25" s="4">
+        <f>IF(PlanLayout!AN25="","",PlanLayout!AN25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO25" s="4">
+        <f>IF(PlanLayout!AO25="","",PlanLayout!AO25&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO25,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO25,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO25,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO25,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="4">
+        <f>IF(PlanLayout!B26="","",PlanLayout!B26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C26" s="4">
+        <f>IF(PlanLayout!C26="","",PlanLayout!C26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D26" s="4">
+        <f>IF(PlanLayout!D26="","",PlanLayout!D26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E26" s="4">
+        <f>IF(PlanLayout!E26="","",PlanLayout!E26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F26" s="4">
+        <f>IF(PlanLayout!F26="","",PlanLayout!F26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G26" s="4">
+        <f>IF(PlanLayout!G26="","",PlanLayout!G26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H26" s="4">
+        <f>IF(PlanLayout!H26="","",PlanLayout!H26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I26" s="4">
+        <f>IF(PlanLayout!I26="","",PlanLayout!I26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J26" s="4">
+        <f>IF(PlanLayout!J26="","",PlanLayout!J26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K26" s="4">
+        <f>IF(PlanLayout!K26="","",PlanLayout!K26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L26" s="4">
+        <f>IF(PlanLayout!L26="","",PlanLayout!L26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M26" s="4">
+        <f>IF(PlanLayout!M26="","",PlanLayout!M26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N26" s="4">
+        <f>IF(PlanLayout!N26="","",PlanLayout!N26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O26" s="4">
+        <f>IF(PlanLayout!O26="","",PlanLayout!O26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P26" s="4">
+        <f>IF(PlanLayout!P26="","",PlanLayout!P26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q26" s="4">
+        <f>IF(PlanLayout!Q26="","",PlanLayout!Q26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R26" s="4">
+        <f>IF(PlanLayout!R26="","",PlanLayout!R26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S26" s="4">
+        <f>IF(PlanLayout!S26="","",PlanLayout!S26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T26" s="4">
+        <f>IF(PlanLayout!T26="","",PlanLayout!T26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U26" s="4">
+        <f>IF(PlanLayout!U26="","",PlanLayout!U26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V26" s="4">
+        <f>IF(PlanLayout!V26="","",PlanLayout!V26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W26" s="4">
+        <f>IF(PlanLayout!W26="","",PlanLayout!W26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X26" s="4">
+        <f>IF(PlanLayout!X26="","",PlanLayout!X26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y26" s="4">
+        <f>IF(PlanLayout!Y26="","",PlanLayout!Y26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z26" s="4">
+        <f>IF(PlanLayout!Z26="","",PlanLayout!Z26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA26" s="4">
+        <f>IF(PlanLayout!AA26="","",PlanLayout!AA26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB26" s="4">
+        <f>IF(PlanLayout!AB26="","",PlanLayout!AB26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC26" s="4">
+        <f>IF(PlanLayout!AC26="","",PlanLayout!AC26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD26" s="4">
+        <f>IF(PlanLayout!AD26="","",PlanLayout!AD26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE26" s="4">
+        <f>IF(PlanLayout!AE26="","",PlanLayout!AE26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF26" s="4">
+        <f>IF(PlanLayout!AF26="","",PlanLayout!AF26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG26" s="4">
+        <f>IF(PlanLayout!AG26="","",PlanLayout!AG26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH26" s="4">
+        <f>IF(PlanLayout!AH26="","",PlanLayout!AH26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI26" s="4">
+        <f>IF(PlanLayout!AI26="","",PlanLayout!AI26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ26" s="4">
+        <f>IF(PlanLayout!AJ26="","",PlanLayout!AJ26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK26" s="4">
+        <f>IF(PlanLayout!AK26="","",PlanLayout!AK26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL26" s="4">
+        <f>IF(PlanLayout!AL26="","",PlanLayout!AL26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM26" s="4">
+        <f>IF(PlanLayout!AM26="","",PlanLayout!AM26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN26" s="4">
+        <f>IF(PlanLayout!AN26="","",PlanLayout!AN26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO26" s="4">
+        <f>IF(PlanLayout!AO26="","",PlanLayout!AO26&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO26,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO26,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO26,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO26,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="4">
+        <f>IF(PlanLayout!B27="","",PlanLayout!B27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C27" s="4">
+        <f>IF(PlanLayout!C27="","",PlanLayout!C27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D27" s="4">
+        <f>IF(PlanLayout!D27="","",PlanLayout!D27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E27" s="4">
+        <f>IF(PlanLayout!E27="","",PlanLayout!E27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F27" s="4">
+        <f>IF(PlanLayout!F27="","",PlanLayout!F27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G27" s="4">
+        <f>IF(PlanLayout!G27="","",PlanLayout!G27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H27" s="4">
+        <f>IF(PlanLayout!H27="","",PlanLayout!H27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I27" s="4">
+        <f>IF(PlanLayout!I27="","",PlanLayout!I27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J27" s="4">
+        <f>IF(PlanLayout!J27="","",PlanLayout!J27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K27" s="4">
+        <f>IF(PlanLayout!K27="","",PlanLayout!K27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L27" s="4">
+        <f>IF(PlanLayout!L27="","",PlanLayout!L27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M27" s="4">
+        <f>IF(PlanLayout!M27="","",PlanLayout!M27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N27" s="4">
+        <f>IF(PlanLayout!N27="","",PlanLayout!N27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O27" s="4">
+        <f>IF(PlanLayout!O27="","",PlanLayout!O27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P27" s="4">
+        <f>IF(PlanLayout!P27="","",PlanLayout!P27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q27" s="4">
+        <f>IF(PlanLayout!Q27="","",PlanLayout!Q27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R27" s="4">
+        <f>IF(PlanLayout!R27="","",PlanLayout!R27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S27" s="4">
+        <f>IF(PlanLayout!S27="","",PlanLayout!S27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T27" s="4">
+        <f>IF(PlanLayout!T27="","",PlanLayout!T27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U27" s="4">
+        <f>IF(PlanLayout!U27="","",PlanLayout!U27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V27" s="4">
+        <f>IF(PlanLayout!V27="","",PlanLayout!V27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W27" s="4">
+        <f>IF(PlanLayout!W27="","",PlanLayout!W27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X27" s="4">
+        <f>IF(PlanLayout!X27="","",PlanLayout!X27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y27" s="4">
+        <f>IF(PlanLayout!Y27="","",PlanLayout!Y27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z27" s="4">
+        <f>IF(PlanLayout!Z27="","",PlanLayout!Z27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA27" s="4">
+        <f>IF(PlanLayout!AA27="","",PlanLayout!AA27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB27" s="4">
+        <f>IF(PlanLayout!AB27="","",PlanLayout!AB27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC27" s="4">
+        <f>IF(PlanLayout!AC27="","",PlanLayout!AC27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD27" s="4">
+        <f>IF(PlanLayout!AD27="","",PlanLayout!AD27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE27" s="4">
+        <f>IF(PlanLayout!AE27="","",PlanLayout!AE27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF27" s="4">
+        <f>IF(PlanLayout!AF27="","",PlanLayout!AF27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG27" s="4">
+        <f>IF(PlanLayout!AG27="","",PlanLayout!AG27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH27" s="4">
+        <f>IF(PlanLayout!AH27="","",PlanLayout!AH27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI27" s="4">
+        <f>IF(PlanLayout!AI27="","",PlanLayout!AI27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ27" s="4">
+        <f>IF(PlanLayout!AJ27="","",PlanLayout!AJ27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK27" s="4">
+        <f>IF(PlanLayout!AK27="","",PlanLayout!AK27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL27" s="4">
+        <f>IF(PlanLayout!AL27="","",PlanLayout!AL27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM27" s="4">
+        <f>IF(PlanLayout!AM27="","",PlanLayout!AM27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN27" s="4">
+        <f>IF(PlanLayout!AN27="","",PlanLayout!AN27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO27" s="4">
+        <f>IF(PlanLayout!AO27="","",PlanLayout!AO27&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO27,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO27,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO27,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO27,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="4">
+        <f>IF(PlanLayout!B28="","",PlanLayout!B28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C28" s="4">
+        <f>IF(PlanLayout!C28="","",PlanLayout!C28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D28" s="4">
+        <f>IF(PlanLayout!D28="","",PlanLayout!D28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E28" s="4">
+        <f>IF(PlanLayout!E28="","",PlanLayout!E28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F28" s="4">
+        <f>IF(PlanLayout!F28="","",PlanLayout!F28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G28" s="4">
+        <f>IF(PlanLayout!G28="","",PlanLayout!G28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H28" s="4">
+        <f>IF(PlanLayout!H28="","",PlanLayout!H28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I28" s="4">
+        <f>IF(PlanLayout!I28="","",PlanLayout!I28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J28" s="4">
+        <f>IF(PlanLayout!J28="","",PlanLayout!J28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K28" s="4">
+        <f>IF(PlanLayout!K28="","",PlanLayout!K28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L28" s="4">
+        <f>IF(PlanLayout!L28="","",PlanLayout!L28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M28" s="4">
+        <f>IF(PlanLayout!M28="","",PlanLayout!M28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N28" s="4">
+        <f>IF(PlanLayout!N28="","",PlanLayout!N28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O28" s="4">
+        <f>IF(PlanLayout!O28="","",PlanLayout!O28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P28" s="4">
+        <f>IF(PlanLayout!P28="","",PlanLayout!P28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q28" s="4">
+        <f>IF(PlanLayout!Q28="","",PlanLayout!Q28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R28" s="4">
+        <f>IF(PlanLayout!R28="","",PlanLayout!R28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S28" s="4">
+        <f>IF(PlanLayout!S28="","",PlanLayout!S28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T28" s="4">
+        <f>IF(PlanLayout!T28="","",PlanLayout!T28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U28" s="4">
+        <f>IF(PlanLayout!U28="","",PlanLayout!U28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V28" s="4">
+        <f>IF(PlanLayout!V28="","",PlanLayout!V28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W28" s="4">
+        <f>IF(PlanLayout!W28="","",PlanLayout!W28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X28" s="4">
+        <f>IF(PlanLayout!X28="","",PlanLayout!X28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y28" s="4">
+        <f>IF(PlanLayout!Y28="","",PlanLayout!Y28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z28" s="4">
+        <f>IF(PlanLayout!Z28="","",PlanLayout!Z28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA28" s="4">
+        <f>IF(PlanLayout!AA28="","",PlanLayout!AA28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB28" s="4">
+        <f>IF(PlanLayout!AB28="","",PlanLayout!AB28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC28" s="4">
+        <f>IF(PlanLayout!AC28="","",PlanLayout!AC28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD28" s="4">
+        <f>IF(PlanLayout!AD28="","",PlanLayout!AD28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE28" s="4">
+        <f>IF(PlanLayout!AE28="","",PlanLayout!AE28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF28" s="4">
+        <f>IF(PlanLayout!AF28="","",PlanLayout!AF28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG28" s="4">
+        <f>IF(PlanLayout!AG28="","",PlanLayout!AG28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH28" s="4">
+        <f>IF(PlanLayout!AH28="","",PlanLayout!AH28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI28" s="4">
+        <f>IF(PlanLayout!AI28="","",PlanLayout!AI28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ28" s="4">
+        <f>IF(PlanLayout!AJ28="","",PlanLayout!AJ28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK28" s="4">
+        <f>IF(PlanLayout!AK28="","",PlanLayout!AK28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL28" s="4">
+        <f>IF(PlanLayout!AL28="","",PlanLayout!AL28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM28" s="4">
+        <f>IF(PlanLayout!AM28="","",PlanLayout!AM28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN28" s="4">
+        <f>IF(PlanLayout!AN28="","",PlanLayout!AN28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO28" s="4">
+        <f>IF(PlanLayout!AO28="","",PlanLayout!AO28&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO28,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO28,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO28,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO28,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="4">
+        <f>IF(PlanLayout!B29="","",PlanLayout!B29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C29" s="4">
+        <f>IF(PlanLayout!C29="","",PlanLayout!C29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D29" s="4">
+        <f>IF(PlanLayout!D29="","",PlanLayout!D29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E29" s="4">
+        <f>IF(PlanLayout!E29="","",PlanLayout!E29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F29" s="4">
+        <f>IF(PlanLayout!F29="","",PlanLayout!F29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G29" s="4">
+        <f>IF(PlanLayout!G29="","",PlanLayout!G29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H29" s="4">
+        <f>IF(PlanLayout!H29="","",PlanLayout!H29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I29" s="4">
+        <f>IF(PlanLayout!I29="","",PlanLayout!I29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J29" s="4">
+        <f>IF(PlanLayout!J29="","",PlanLayout!J29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K29" s="4">
+        <f>IF(PlanLayout!K29="","",PlanLayout!K29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L29" s="4">
+        <f>IF(PlanLayout!L29="","",PlanLayout!L29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M29" s="4">
+        <f>IF(PlanLayout!M29="","",PlanLayout!M29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N29" s="4">
+        <f>IF(PlanLayout!N29="","",PlanLayout!N29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O29" s="4">
+        <f>IF(PlanLayout!O29="","",PlanLayout!O29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P29" s="4">
+        <f>IF(PlanLayout!P29="","",PlanLayout!P29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q29" s="4">
+        <f>IF(PlanLayout!Q29="","",PlanLayout!Q29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R29" s="4">
+        <f>IF(PlanLayout!R29="","",PlanLayout!R29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S29" s="4">
+        <f>IF(PlanLayout!S29="","",PlanLayout!S29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T29" s="4">
+        <f>IF(PlanLayout!T29="","",PlanLayout!T29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U29" s="4">
+        <f>IF(PlanLayout!U29="","",PlanLayout!U29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V29" s="4">
+        <f>IF(PlanLayout!V29="","",PlanLayout!V29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W29" s="4">
+        <f>IF(PlanLayout!W29="","",PlanLayout!W29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X29" s="4">
+        <f>IF(PlanLayout!X29="","",PlanLayout!X29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y29" s="4">
+        <f>IF(PlanLayout!Y29="","",PlanLayout!Y29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z29" s="4">
+        <f>IF(PlanLayout!Z29="","",PlanLayout!Z29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA29" s="4">
+        <f>IF(PlanLayout!AA29="","",PlanLayout!AA29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB29" s="4">
+        <f>IF(PlanLayout!AB29="","",PlanLayout!AB29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC29" s="4">
+        <f>IF(PlanLayout!AC29="","",PlanLayout!AC29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD29" s="4">
+        <f>IF(PlanLayout!AD29="","",PlanLayout!AD29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE29" s="4">
+        <f>IF(PlanLayout!AE29="","",PlanLayout!AE29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF29" s="4">
+        <f>IF(PlanLayout!AF29="","",PlanLayout!AF29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG29" s="4">
+        <f>IF(PlanLayout!AG29="","",PlanLayout!AG29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH29" s="4">
+        <f>IF(PlanLayout!AH29="","",PlanLayout!AH29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI29" s="4">
+        <f>IF(PlanLayout!AI29="","",PlanLayout!AI29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ29" s="4">
+        <f>IF(PlanLayout!AJ29="","",PlanLayout!AJ29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK29" s="4">
+        <f>IF(PlanLayout!AK29="","",PlanLayout!AK29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL29" s="4">
+        <f>IF(PlanLayout!AL29="","",PlanLayout!AL29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM29" s="4">
+        <f>IF(PlanLayout!AM29="","",PlanLayout!AM29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN29" s="4">
+        <f>IF(PlanLayout!AN29="","",PlanLayout!AN29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO29" s="4">
+        <f>IF(PlanLayout!AO29="","",PlanLayout!AO29&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO29,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO29,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO29,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO29,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="4">
+        <f>IF(PlanLayout!B30="","",PlanLayout!B30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C30" s="4">
+        <f>IF(PlanLayout!C30="","",PlanLayout!C30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D30" s="4">
+        <f>IF(PlanLayout!D30="","",PlanLayout!D30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E30" s="4">
+        <f>IF(PlanLayout!E30="","",PlanLayout!E30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F30" s="4">
+        <f>IF(PlanLayout!F30="","",PlanLayout!F30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G30" s="4">
+        <f>IF(PlanLayout!G30="","",PlanLayout!G30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H30" s="4">
+        <f>IF(PlanLayout!H30="","",PlanLayout!H30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I30" s="4">
+        <f>IF(PlanLayout!I30="","",PlanLayout!I30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J30" s="4">
+        <f>IF(PlanLayout!J30="","",PlanLayout!J30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K30" s="4">
+        <f>IF(PlanLayout!K30="","",PlanLayout!K30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L30" s="4">
+        <f>IF(PlanLayout!L30="","",PlanLayout!L30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M30" s="4">
+        <f>IF(PlanLayout!M30="","",PlanLayout!M30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N30" s="4">
+        <f>IF(PlanLayout!N30="","",PlanLayout!N30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O30" s="4">
+        <f>IF(PlanLayout!O30="","",PlanLayout!O30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P30" s="4">
+        <f>IF(PlanLayout!P30="","",PlanLayout!P30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q30" s="4">
+        <f>IF(PlanLayout!Q30="","",PlanLayout!Q30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R30" s="4">
+        <f>IF(PlanLayout!R30="","",PlanLayout!R30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S30" s="4">
+        <f>IF(PlanLayout!S30="","",PlanLayout!S30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T30" s="4">
+        <f>IF(PlanLayout!T30="","",PlanLayout!T30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U30" s="4">
+        <f>IF(PlanLayout!U30="","",PlanLayout!U30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V30" s="4">
+        <f>IF(PlanLayout!V30="","",PlanLayout!V30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W30" s="4">
+        <f>IF(PlanLayout!W30="","",PlanLayout!W30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X30" s="4">
+        <f>IF(PlanLayout!X30="","",PlanLayout!X30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y30" s="4">
+        <f>IF(PlanLayout!Y30="","",PlanLayout!Y30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z30" s="4">
+        <f>IF(PlanLayout!Z30="","",PlanLayout!Z30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA30" s="4">
+        <f>IF(PlanLayout!AA30="","",PlanLayout!AA30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB30" s="4">
+        <f>IF(PlanLayout!AB30="","",PlanLayout!AB30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC30" s="4">
+        <f>IF(PlanLayout!AC30="","",PlanLayout!AC30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD30" s="4">
+        <f>IF(PlanLayout!AD30="","",PlanLayout!AD30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE30" s="4">
+        <f>IF(PlanLayout!AE30="","",PlanLayout!AE30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF30" s="4">
+        <f>IF(PlanLayout!AF30="","",PlanLayout!AF30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG30" s="4">
+        <f>IF(PlanLayout!AG30="","",PlanLayout!AG30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH30" s="4">
+        <f>IF(PlanLayout!AH30="","",PlanLayout!AH30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI30" s="4">
+        <f>IF(PlanLayout!AI30="","",PlanLayout!AI30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ30" s="4">
+        <f>IF(PlanLayout!AJ30="","",PlanLayout!AJ30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK30" s="4">
+        <f>IF(PlanLayout!AK30="","",PlanLayout!AK30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL30" s="4">
+        <f>IF(PlanLayout!AL30="","",PlanLayout!AL30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM30" s="4">
+        <f>IF(PlanLayout!AM30="","",PlanLayout!AM30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN30" s="4">
+        <f>IF(PlanLayout!AN30="","",PlanLayout!AN30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO30" s="4">
+        <f>IF(PlanLayout!AO30="","",PlanLayout!AO30&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO30,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO30,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO30,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO30,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="4">
+        <f>IF(PlanLayout!B31="","",PlanLayout!B31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C31" s="4">
+        <f>IF(PlanLayout!C31="","",PlanLayout!C31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D31" s="4">
+        <f>IF(PlanLayout!D31="","",PlanLayout!D31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E31" s="4">
+        <f>IF(PlanLayout!E31="","",PlanLayout!E31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F31" s="4">
+        <f>IF(PlanLayout!F31="","",PlanLayout!F31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G31" s="4">
+        <f>IF(PlanLayout!G31="","",PlanLayout!G31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H31" s="4">
+        <f>IF(PlanLayout!H31="","",PlanLayout!H31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I31" s="4">
+        <f>IF(PlanLayout!I31="","",PlanLayout!I31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J31" s="4">
+        <f>IF(PlanLayout!J31="","",PlanLayout!J31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K31" s="4">
+        <f>IF(PlanLayout!K31="","",PlanLayout!K31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L31" s="4">
+        <f>IF(PlanLayout!L31="","",PlanLayout!L31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M31" s="4">
+        <f>IF(PlanLayout!M31="","",PlanLayout!M31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N31" s="4">
+        <f>IF(PlanLayout!N31="","",PlanLayout!N31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O31" s="4">
+        <f>IF(PlanLayout!O31="","",PlanLayout!O31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P31" s="4">
+        <f>IF(PlanLayout!P31="","",PlanLayout!P31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q31" s="4">
+        <f>IF(PlanLayout!Q31="","",PlanLayout!Q31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R31" s="4">
+        <f>IF(PlanLayout!R31="","",PlanLayout!R31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S31" s="4">
+        <f>IF(PlanLayout!S31="","",PlanLayout!S31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T31" s="4">
+        <f>IF(PlanLayout!T31="","",PlanLayout!T31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U31" s="4">
+        <f>IF(PlanLayout!U31="","",PlanLayout!U31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V31" s="4">
+        <f>IF(PlanLayout!V31="","",PlanLayout!V31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W31" s="4">
+        <f>IF(PlanLayout!W31="","",PlanLayout!W31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X31" s="4">
+        <f>IF(PlanLayout!X31="","",PlanLayout!X31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y31" s="4">
+        <f>IF(PlanLayout!Y31="","",PlanLayout!Y31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z31" s="4">
+        <f>IF(PlanLayout!Z31="","",PlanLayout!Z31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA31" s="4">
+        <f>IF(PlanLayout!AA31="","",PlanLayout!AA31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB31" s="4">
+        <f>IF(PlanLayout!AB31="","",PlanLayout!AB31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC31" s="4">
+        <f>IF(PlanLayout!AC31="","",PlanLayout!AC31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD31" s="4">
+        <f>IF(PlanLayout!AD31="","",PlanLayout!AD31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE31" s="4">
+        <f>IF(PlanLayout!AE31="","",PlanLayout!AE31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF31" s="4">
+        <f>IF(PlanLayout!AF31="","",PlanLayout!AF31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG31" s="4">
+        <f>IF(PlanLayout!AG31="","",PlanLayout!AG31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH31" s="4">
+        <f>IF(PlanLayout!AH31="","",PlanLayout!AH31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI31" s="4">
+        <f>IF(PlanLayout!AI31="","",PlanLayout!AI31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ31" s="4">
+        <f>IF(PlanLayout!AJ31="","",PlanLayout!AJ31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK31" s="4">
+        <f>IF(PlanLayout!AK31="","",PlanLayout!AK31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL31" s="4">
+        <f>IF(PlanLayout!AL31="","",PlanLayout!AL31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM31" s="4">
+        <f>IF(PlanLayout!AM31="","",PlanLayout!AM31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN31" s="4">
+        <f>IF(PlanLayout!AN31="","",PlanLayout!AN31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO31" s="4">
+        <f>IF(PlanLayout!AO31="","",PlanLayout!AO31&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO31,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO31,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO31,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO31,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" s="4">
+        <f>IF(PlanLayout!B32="","",PlanLayout!B32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C32" s="4">
+        <f>IF(PlanLayout!C32="","",PlanLayout!C32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D32" s="4">
+        <f>IF(PlanLayout!D32="","",PlanLayout!D32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E32" s="4">
+        <f>IF(PlanLayout!E32="","",PlanLayout!E32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F32" s="4">
+        <f>IF(PlanLayout!F32="","",PlanLayout!F32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G32" s="4">
+        <f>IF(PlanLayout!G32="","",PlanLayout!G32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H32" s="4">
+        <f>IF(PlanLayout!H32="","",PlanLayout!H32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I32" s="4">
+        <f>IF(PlanLayout!I32="","",PlanLayout!I32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J32" s="4">
+        <f>IF(PlanLayout!J32="","",PlanLayout!J32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K32" s="4">
+        <f>IF(PlanLayout!K32="","",PlanLayout!K32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L32" s="4">
+        <f>IF(PlanLayout!L32="","",PlanLayout!L32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M32" s="4">
+        <f>IF(PlanLayout!M32="","",PlanLayout!M32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N32" s="4">
+        <f>IF(PlanLayout!N32="","",PlanLayout!N32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O32" s="4">
+        <f>IF(PlanLayout!O32="","",PlanLayout!O32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P32" s="4">
+        <f>IF(PlanLayout!P32="","",PlanLayout!P32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q32" s="4">
+        <f>IF(PlanLayout!Q32="","",PlanLayout!Q32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R32" s="4">
+        <f>IF(PlanLayout!R32="","",PlanLayout!R32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S32" s="4">
+        <f>IF(PlanLayout!S32="","",PlanLayout!S32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T32" s="4">
+        <f>IF(PlanLayout!T32="","",PlanLayout!T32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U32" s="4">
+        <f>IF(PlanLayout!U32="","",PlanLayout!U32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V32" s="4">
+        <f>IF(PlanLayout!V32="","",PlanLayout!V32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W32" s="4">
+        <f>IF(PlanLayout!W32="","",PlanLayout!W32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X32" s="4">
+        <f>IF(PlanLayout!X32="","",PlanLayout!X32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y32" s="4">
+        <f>IF(PlanLayout!Y32="","",PlanLayout!Y32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z32" s="4">
+        <f>IF(PlanLayout!Z32="","",PlanLayout!Z32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA32" s="4">
+        <f>IF(PlanLayout!AA32="","",PlanLayout!AA32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB32" s="4">
+        <f>IF(PlanLayout!AB32="","",PlanLayout!AB32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC32" s="4">
+        <f>IF(PlanLayout!AC32="","",PlanLayout!AC32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD32" s="4">
+        <f>IF(PlanLayout!AD32="","",PlanLayout!AD32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE32" s="4">
+        <f>IF(PlanLayout!AE32="","",PlanLayout!AE32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF32" s="4">
+        <f>IF(PlanLayout!AF32="","",PlanLayout!AF32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG32" s="4">
+        <f>IF(PlanLayout!AG32="","",PlanLayout!AG32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH32" s="4">
+        <f>IF(PlanLayout!AH32="","",PlanLayout!AH32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI32" s="4">
+        <f>IF(PlanLayout!AI32="","",PlanLayout!AI32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ32" s="4">
+        <f>IF(PlanLayout!AJ32="","",PlanLayout!AJ32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK32" s="4">
+        <f>IF(PlanLayout!AK32="","",PlanLayout!AK32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL32" s="4">
+        <f>IF(PlanLayout!AL32="","",PlanLayout!AL32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM32" s="4">
+        <f>IF(PlanLayout!AM32="","",PlanLayout!AM32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN32" s="4">
+        <f>IF(PlanLayout!AN32="","",PlanLayout!AN32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO32" s="4">
+        <f>IF(PlanLayout!AO32="","",PlanLayout!AO32&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO32,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO32,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO32,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO32,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="4">
+        <f>IF(PlanLayout!B33="","",PlanLayout!B33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C33" s="4">
+        <f>IF(PlanLayout!C33="","",PlanLayout!C33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D33" s="4">
+        <f>IF(PlanLayout!D33="","",PlanLayout!D33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E33" s="4">
+        <f>IF(PlanLayout!E33="","",PlanLayout!E33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F33" s="4">
+        <f>IF(PlanLayout!F33="","",PlanLayout!F33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G33" s="4">
+        <f>IF(PlanLayout!G33="","",PlanLayout!G33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H33" s="4">
+        <f>IF(PlanLayout!H33="","",PlanLayout!H33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I33" s="4">
+        <f>IF(PlanLayout!I33="","",PlanLayout!I33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J33" s="4">
+        <f>IF(PlanLayout!J33="","",PlanLayout!J33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K33" s="4">
+        <f>IF(PlanLayout!K33="","",PlanLayout!K33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L33" s="4">
+        <f>IF(PlanLayout!L33="","",PlanLayout!L33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M33" s="4">
+        <f>IF(PlanLayout!M33="","",PlanLayout!M33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N33" s="4">
+        <f>IF(PlanLayout!N33="","",PlanLayout!N33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O33" s="4">
+        <f>IF(PlanLayout!O33="","",PlanLayout!O33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P33" s="4">
+        <f>IF(PlanLayout!P33="","",PlanLayout!P33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q33" s="4">
+        <f>IF(PlanLayout!Q33="","",PlanLayout!Q33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R33" s="4">
+        <f>IF(PlanLayout!R33="","",PlanLayout!R33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S33" s="4">
+        <f>IF(PlanLayout!S33="","",PlanLayout!S33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T33" s="4">
+        <f>IF(PlanLayout!T33="","",PlanLayout!T33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U33" s="4">
+        <f>IF(PlanLayout!U33="","",PlanLayout!U33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V33" s="4">
+        <f>IF(PlanLayout!V33="","",PlanLayout!V33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W33" s="4">
+        <f>IF(PlanLayout!W33="","",PlanLayout!W33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X33" s="4">
+        <f>IF(PlanLayout!X33="","",PlanLayout!X33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y33" s="4">
+        <f>IF(PlanLayout!Y33="","",PlanLayout!Y33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z33" s="4">
+        <f>IF(PlanLayout!Z33="","",PlanLayout!Z33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA33" s="4">
+        <f>IF(PlanLayout!AA33="","",PlanLayout!AA33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB33" s="4">
+        <f>IF(PlanLayout!AB33="","",PlanLayout!AB33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC33" s="4">
+        <f>IF(PlanLayout!AC33="","",PlanLayout!AC33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD33" s="4">
+        <f>IF(PlanLayout!AD33="","",PlanLayout!AD33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE33" s="4">
+        <f>IF(PlanLayout!AE33="","",PlanLayout!AE33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF33" s="4">
+        <f>IF(PlanLayout!AF33="","",PlanLayout!AF33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG33" s="4">
+        <f>IF(PlanLayout!AG33="","",PlanLayout!AG33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH33" s="4">
+        <f>IF(PlanLayout!AH33="","",PlanLayout!AH33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI33" s="4">
+        <f>IF(PlanLayout!AI33="","",PlanLayout!AI33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ33" s="4">
+        <f>IF(PlanLayout!AJ33="","",PlanLayout!AJ33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK33" s="4">
+        <f>IF(PlanLayout!AK33="","",PlanLayout!AK33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL33" s="4">
+        <f>IF(PlanLayout!AL33="","",PlanLayout!AL33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM33" s="4">
+        <f>IF(PlanLayout!AM33="","",PlanLayout!AM33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN33" s="4">
+        <f>IF(PlanLayout!AN33="","",PlanLayout!AN33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO33" s="4">
+        <f>IF(PlanLayout!AO33="","",PlanLayout!AO33&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO33,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO33,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO33,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO33,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="4">
+        <f>IF(PlanLayout!B34="","",PlanLayout!B34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C34" s="4">
+        <f>IF(PlanLayout!C34="","",PlanLayout!C34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D34" s="4">
+        <f>IF(PlanLayout!D34="","",PlanLayout!D34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E34" s="4">
+        <f>IF(PlanLayout!E34="","",PlanLayout!E34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F34" s="4">
+        <f>IF(PlanLayout!F34="","",PlanLayout!F34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G34" s="4">
+        <f>IF(PlanLayout!G34="","",PlanLayout!G34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H34" s="4">
+        <f>IF(PlanLayout!H34="","",PlanLayout!H34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I34" s="4">
+        <f>IF(PlanLayout!I34="","",PlanLayout!I34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J34" s="4">
+        <f>IF(PlanLayout!J34="","",PlanLayout!J34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K34" s="4">
+        <f>IF(PlanLayout!K34="","",PlanLayout!K34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L34" s="4">
+        <f>IF(PlanLayout!L34="","",PlanLayout!L34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M34" s="4">
+        <f>IF(PlanLayout!M34="","",PlanLayout!M34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N34" s="4">
+        <f>IF(PlanLayout!N34="","",PlanLayout!N34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O34" s="4">
+        <f>IF(PlanLayout!O34="","",PlanLayout!O34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P34" s="4">
+        <f>IF(PlanLayout!P34="","",PlanLayout!P34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q34" s="4">
+        <f>IF(PlanLayout!Q34="","",PlanLayout!Q34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R34" s="4">
+        <f>IF(PlanLayout!R34="","",PlanLayout!R34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S34" s="4">
+        <f>IF(PlanLayout!S34="","",PlanLayout!S34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T34" s="4">
+        <f>IF(PlanLayout!T34="","",PlanLayout!T34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U34" s="4">
+        <f>IF(PlanLayout!U34="","",PlanLayout!U34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V34" s="4">
+        <f>IF(PlanLayout!V34="","",PlanLayout!V34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W34" s="4">
+        <f>IF(PlanLayout!W34="","",PlanLayout!W34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X34" s="4">
+        <f>IF(PlanLayout!X34="","",PlanLayout!X34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y34" s="4">
+        <f>IF(PlanLayout!Y34="","",PlanLayout!Y34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z34" s="4">
+        <f>IF(PlanLayout!Z34="","",PlanLayout!Z34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA34" s="4">
+        <f>IF(PlanLayout!AA34="","",PlanLayout!AA34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB34" s="4">
+        <f>IF(PlanLayout!AB34="","",PlanLayout!AB34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC34" s="4">
+        <f>IF(PlanLayout!AC34="","",PlanLayout!AC34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD34" s="4">
+        <f>IF(PlanLayout!AD34="","",PlanLayout!AD34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE34" s="4">
+        <f>IF(PlanLayout!AE34="","",PlanLayout!AE34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF34" s="4">
+        <f>IF(PlanLayout!AF34="","",PlanLayout!AF34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG34" s="4">
+        <f>IF(PlanLayout!AG34="","",PlanLayout!AG34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH34" s="4">
+        <f>IF(PlanLayout!AH34="","",PlanLayout!AH34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI34" s="4">
+        <f>IF(PlanLayout!AI34="","",PlanLayout!AI34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ34" s="4">
+        <f>IF(PlanLayout!AJ34="","",PlanLayout!AJ34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK34" s="4">
+        <f>IF(PlanLayout!AK34="","",PlanLayout!AK34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL34" s="4">
+        <f>IF(PlanLayout!AL34="","",PlanLayout!AL34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM34" s="4">
+        <f>IF(PlanLayout!AM34="","",PlanLayout!AM34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN34" s="4">
+        <f>IF(PlanLayout!AN34="","",PlanLayout!AN34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO34" s="4">
+        <f>IF(PlanLayout!AO34="","",PlanLayout!AO34&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO34,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO34,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO34,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO34,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="B35" s="4">
+        <f>IF(PlanLayout!B35="","",PlanLayout!B35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C35" s="4">
+        <f>IF(PlanLayout!C35="","",PlanLayout!C35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D35" s="4">
+        <f>IF(PlanLayout!D35="","",PlanLayout!D35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E35" s="4">
+        <f>IF(PlanLayout!E35="","",PlanLayout!E35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F35" s="4">
+        <f>IF(PlanLayout!F35="","",PlanLayout!F35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G35" s="4">
+        <f>IF(PlanLayout!G35="","",PlanLayout!G35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H35" s="4">
+        <f>IF(PlanLayout!H35="","",PlanLayout!H35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I35" s="4">
+        <f>IF(PlanLayout!I35="","",PlanLayout!I35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J35" s="4">
+        <f>IF(PlanLayout!J35="","",PlanLayout!J35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K35" s="4">
+        <f>IF(PlanLayout!K35="","",PlanLayout!K35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L35" s="4">
+        <f>IF(PlanLayout!L35="","",PlanLayout!L35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M35" s="4">
+        <f>IF(PlanLayout!M35="","",PlanLayout!M35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N35" s="4">
+        <f>IF(PlanLayout!N35="","",PlanLayout!N35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O35" s="4">
+        <f>IF(PlanLayout!O35="","",PlanLayout!O35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P35" s="4">
+        <f>IF(PlanLayout!P35="","",PlanLayout!P35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q35" s="4">
+        <f>IF(PlanLayout!Q35="","",PlanLayout!Q35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R35" s="4">
+        <f>IF(PlanLayout!R35="","",PlanLayout!R35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S35" s="4">
+        <f>IF(PlanLayout!S35="","",PlanLayout!S35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T35" s="4">
+        <f>IF(PlanLayout!T35="","",PlanLayout!T35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U35" s="4">
+        <f>IF(PlanLayout!U35="","",PlanLayout!U35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V35" s="4">
+        <f>IF(PlanLayout!V35="","",PlanLayout!V35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W35" s="4">
+        <f>IF(PlanLayout!W35="","",PlanLayout!W35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X35" s="4">
+        <f>IF(PlanLayout!X35="","",PlanLayout!X35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y35" s="4">
+        <f>IF(PlanLayout!Y35="","",PlanLayout!Y35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z35" s="4">
+        <f>IF(PlanLayout!Z35="","",PlanLayout!Z35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA35" s="4">
+        <f>IF(PlanLayout!AA35="","",PlanLayout!AA35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB35" s="4">
+        <f>IF(PlanLayout!AB35="","",PlanLayout!AB35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC35" s="4">
+        <f>IF(PlanLayout!AC35="","",PlanLayout!AC35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD35" s="4">
+        <f>IF(PlanLayout!AD35="","",PlanLayout!AD35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE35" s="4">
+        <f>IF(PlanLayout!AE35="","",PlanLayout!AE35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF35" s="4">
+        <f>IF(PlanLayout!AF35="","",PlanLayout!AF35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG35" s="4">
+        <f>IF(PlanLayout!AG35="","",PlanLayout!AG35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH35" s="4">
+        <f>IF(PlanLayout!AH35="","",PlanLayout!AH35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI35" s="4">
+        <f>IF(PlanLayout!AI35="","",PlanLayout!AI35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ35" s="4">
+        <f>IF(PlanLayout!AJ35="","",PlanLayout!AJ35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK35" s="4">
+        <f>IF(PlanLayout!AK35="","",PlanLayout!AK35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL35" s="4">
+        <f>IF(PlanLayout!AL35="","",PlanLayout!AL35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM35" s="4">
+        <f>IF(PlanLayout!AM35="","",PlanLayout!AM35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN35" s="4">
+        <f>IF(PlanLayout!AN35="","",PlanLayout!AN35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO35" s="4">
+        <f>IF(PlanLayout!AO35="","",PlanLayout!AO35&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO35,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO35,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO35,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO35,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="B36" s="4">
+        <f>IF(PlanLayout!B36="","",PlanLayout!B36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C36" s="4">
+        <f>IF(PlanLayout!C36="","",PlanLayout!C36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D36" s="4">
+        <f>IF(PlanLayout!D36="","",PlanLayout!D36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E36" s="4">
+        <f>IF(PlanLayout!E36="","",PlanLayout!E36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F36" s="4">
+        <f>IF(PlanLayout!F36="","",PlanLayout!F36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G36" s="4">
+        <f>IF(PlanLayout!G36="","",PlanLayout!G36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H36" s="4">
+        <f>IF(PlanLayout!H36="","",PlanLayout!H36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I36" s="4">
+        <f>IF(PlanLayout!I36="","",PlanLayout!I36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J36" s="4">
+        <f>IF(PlanLayout!J36="","",PlanLayout!J36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K36" s="4">
+        <f>IF(PlanLayout!K36="","",PlanLayout!K36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L36" s="4">
+        <f>IF(PlanLayout!L36="","",PlanLayout!L36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M36" s="4">
+        <f>IF(PlanLayout!M36="","",PlanLayout!M36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N36" s="4">
+        <f>IF(PlanLayout!N36="","",PlanLayout!N36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O36" s="4">
+        <f>IF(PlanLayout!O36="","",PlanLayout!O36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P36" s="4">
+        <f>IF(PlanLayout!P36="","",PlanLayout!P36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q36" s="4">
+        <f>IF(PlanLayout!Q36="","",PlanLayout!Q36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R36" s="4">
+        <f>IF(PlanLayout!R36="","",PlanLayout!R36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S36" s="4">
+        <f>IF(PlanLayout!S36="","",PlanLayout!S36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T36" s="4">
+        <f>IF(PlanLayout!T36="","",PlanLayout!T36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U36" s="4">
+        <f>IF(PlanLayout!U36="","",PlanLayout!U36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V36" s="4">
+        <f>IF(PlanLayout!V36="","",PlanLayout!V36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W36" s="4">
+        <f>IF(PlanLayout!W36="","",PlanLayout!W36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X36" s="4">
+        <f>IF(PlanLayout!X36="","",PlanLayout!X36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y36" s="4">
+        <f>IF(PlanLayout!Y36="","",PlanLayout!Y36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z36" s="4">
+        <f>IF(PlanLayout!Z36="","",PlanLayout!Z36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA36" s="4">
+        <f>IF(PlanLayout!AA36="","",PlanLayout!AA36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB36" s="4">
+        <f>IF(PlanLayout!AB36="","",PlanLayout!AB36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC36" s="4">
+        <f>IF(PlanLayout!AC36="","",PlanLayout!AC36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD36" s="4">
+        <f>IF(PlanLayout!AD36="","",PlanLayout!AD36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE36" s="4">
+        <f>IF(PlanLayout!AE36="","",PlanLayout!AE36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF36" s="4">
+        <f>IF(PlanLayout!AF36="","",PlanLayout!AF36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG36" s="4">
+        <f>IF(PlanLayout!AG36="","",PlanLayout!AG36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH36" s="4">
+        <f>IF(PlanLayout!AH36="","",PlanLayout!AH36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI36" s="4">
+        <f>IF(PlanLayout!AI36="","",PlanLayout!AI36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ36" s="4">
+        <f>IF(PlanLayout!AJ36="","",PlanLayout!AJ36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK36" s="4">
+        <f>IF(PlanLayout!AK36="","",PlanLayout!AK36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL36" s="4">
+        <f>IF(PlanLayout!AL36="","",PlanLayout!AL36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM36" s="4">
+        <f>IF(PlanLayout!AM36="","",PlanLayout!AM36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN36" s="4">
+        <f>IF(PlanLayout!AN36="","",PlanLayout!AN36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO36" s="4">
+        <f>IF(PlanLayout!AO36="","",PlanLayout!AO36&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO36,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO36,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO36,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO36,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="B37" s="4">
+        <f>IF(PlanLayout!B37="","",PlanLayout!B37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C37" s="4">
+        <f>IF(PlanLayout!C37="","",PlanLayout!C37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D37" s="4">
+        <f>IF(PlanLayout!D37="","",PlanLayout!D37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E37" s="4">
+        <f>IF(PlanLayout!E37="","",PlanLayout!E37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F37" s="4">
+        <f>IF(PlanLayout!F37="","",PlanLayout!F37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G37" s="4">
+        <f>IF(PlanLayout!G37="","",PlanLayout!G37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H37" s="4">
+        <f>IF(PlanLayout!H37="","",PlanLayout!H37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I37" s="4">
+        <f>IF(PlanLayout!I37="","",PlanLayout!I37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J37" s="4">
+        <f>IF(PlanLayout!J37="","",PlanLayout!J37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K37" s="4">
+        <f>IF(PlanLayout!K37="","",PlanLayout!K37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L37" s="4">
+        <f>IF(PlanLayout!L37="","",PlanLayout!L37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M37" s="4">
+        <f>IF(PlanLayout!M37="","",PlanLayout!M37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N37" s="4">
+        <f>IF(PlanLayout!N37="","",PlanLayout!N37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O37" s="4">
+        <f>IF(PlanLayout!O37="","",PlanLayout!O37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P37" s="4">
+        <f>IF(PlanLayout!P37="","",PlanLayout!P37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q37" s="4">
+        <f>IF(PlanLayout!Q37="","",PlanLayout!Q37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R37" s="4">
+        <f>IF(PlanLayout!R37="","",PlanLayout!R37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S37" s="4">
+        <f>IF(PlanLayout!S37="","",PlanLayout!S37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T37" s="4">
+        <f>IF(PlanLayout!T37="","",PlanLayout!T37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U37" s="4">
+        <f>IF(PlanLayout!U37="","",PlanLayout!U37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V37" s="4">
+        <f>IF(PlanLayout!V37="","",PlanLayout!V37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W37" s="4">
+        <f>IF(PlanLayout!W37="","",PlanLayout!W37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X37" s="4">
+        <f>IF(PlanLayout!X37="","",PlanLayout!X37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y37" s="4">
+        <f>IF(PlanLayout!Y37="","",PlanLayout!Y37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z37" s="4">
+        <f>IF(PlanLayout!Z37="","",PlanLayout!Z37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA37" s="4">
+        <f>IF(PlanLayout!AA37="","",PlanLayout!AA37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB37" s="4">
+        <f>IF(PlanLayout!AB37="","",PlanLayout!AB37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC37" s="4">
+        <f>IF(PlanLayout!AC37="","",PlanLayout!AC37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD37" s="4">
+        <f>IF(PlanLayout!AD37="","",PlanLayout!AD37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE37" s="4">
+        <f>IF(PlanLayout!AE37="","",PlanLayout!AE37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF37" s="4">
+        <f>IF(PlanLayout!AF37="","",PlanLayout!AF37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG37" s="4">
+        <f>IF(PlanLayout!AG37="","",PlanLayout!AG37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH37" s="4">
+        <f>IF(PlanLayout!AH37="","",PlanLayout!AH37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI37" s="4">
+        <f>IF(PlanLayout!AI37="","",PlanLayout!AI37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ37" s="4">
+        <f>IF(PlanLayout!AJ37="","",PlanLayout!AJ37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK37" s="4">
+        <f>IF(PlanLayout!AK37="","",PlanLayout!AK37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL37" s="4">
+        <f>IF(PlanLayout!AL37="","",PlanLayout!AL37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM37" s="4">
+        <f>IF(PlanLayout!AM37="","",PlanLayout!AM37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN37" s="4">
+        <f>IF(PlanLayout!AN37="","",PlanLayout!AN37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO37" s="4">
+        <f>IF(PlanLayout!AO37="","",PlanLayout!AO37&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO37,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO37,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO37,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO37,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="B38" s="4">
+        <f>IF(PlanLayout!B38="","",PlanLayout!B38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C38" s="4">
+        <f>IF(PlanLayout!C38="","",PlanLayout!C38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D38" s="4">
+        <f>IF(PlanLayout!D38="","",PlanLayout!D38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E38" s="4">
+        <f>IF(PlanLayout!E38="","",PlanLayout!E38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F38" s="4">
+        <f>IF(PlanLayout!F38="","",PlanLayout!F38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G38" s="4">
+        <f>IF(PlanLayout!G38="","",PlanLayout!G38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H38" s="4">
+        <f>IF(PlanLayout!H38="","",PlanLayout!H38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I38" s="4">
+        <f>IF(PlanLayout!I38="","",PlanLayout!I38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J38" s="4">
+        <f>IF(PlanLayout!J38="","",PlanLayout!J38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K38" s="4">
+        <f>IF(PlanLayout!K38="","",PlanLayout!K38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L38" s="4">
+        <f>IF(PlanLayout!L38="","",PlanLayout!L38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M38" s="4">
+        <f>IF(PlanLayout!M38="","",PlanLayout!M38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N38" s="4">
+        <f>IF(PlanLayout!N38="","",PlanLayout!N38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O38" s="4">
+        <f>IF(PlanLayout!O38="","",PlanLayout!O38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P38" s="4">
+        <f>IF(PlanLayout!P38="","",PlanLayout!P38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q38" s="4">
+        <f>IF(PlanLayout!Q38="","",PlanLayout!Q38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R38" s="4">
+        <f>IF(PlanLayout!R38="","",PlanLayout!R38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S38" s="4">
+        <f>IF(PlanLayout!S38="","",PlanLayout!S38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T38" s="4">
+        <f>IF(PlanLayout!T38="","",PlanLayout!T38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U38" s="4">
+        <f>IF(PlanLayout!U38="","",PlanLayout!U38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V38" s="4">
+        <f>IF(PlanLayout!V38="","",PlanLayout!V38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W38" s="4">
+        <f>IF(PlanLayout!W38="","",PlanLayout!W38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X38" s="4">
+        <f>IF(PlanLayout!X38="","",PlanLayout!X38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y38" s="4">
+        <f>IF(PlanLayout!Y38="","",PlanLayout!Y38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z38" s="4">
+        <f>IF(PlanLayout!Z38="","",PlanLayout!Z38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA38" s="4">
+        <f>IF(PlanLayout!AA38="","",PlanLayout!AA38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB38" s="4">
+        <f>IF(PlanLayout!AB38="","",PlanLayout!AB38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC38" s="4">
+        <f>IF(PlanLayout!AC38="","",PlanLayout!AC38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD38" s="4">
+        <f>IF(PlanLayout!AD38="","",PlanLayout!AD38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE38" s="4">
+        <f>IF(PlanLayout!AE38="","",PlanLayout!AE38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF38" s="4">
+        <f>IF(PlanLayout!AF38="","",PlanLayout!AF38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG38" s="4">
+        <f>IF(PlanLayout!AG38="","",PlanLayout!AG38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH38" s="4">
+        <f>IF(PlanLayout!AH38="","",PlanLayout!AH38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI38" s="4">
+        <f>IF(PlanLayout!AI38="","",PlanLayout!AI38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ38" s="4">
+        <f>IF(PlanLayout!AJ38="","",PlanLayout!AJ38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK38" s="4">
+        <f>IF(PlanLayout!AK38="","",PlanLayout!AK38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL38" s="4">
+        <f>IF(PlanLayout!AL38="","",PlanLayout!AL38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM38" s="4">
+        <f>IF(PlanLayout!AM38="","",PlanLayout!AM38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN38" s="4">
+        <f>IF(PlanLayout!AN38="","",PlanLayout!AN38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO38" s="4">
+        <f>IF(PlanLayout!AO38="","",PlanLayout!AO38&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO38,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO38,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO38,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO38,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="B39" s="4">
+        <f>IF(PlanLayout!B39="","",PlanLayout!B39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C39" s="4">
+        <f>IF(PlanLayout!C39="","",PlanLayout!C39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D39" s="4">
+        <f>IF(PlanLayout!D39="","",PlanLayout!D39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E39" s="4">
+        <f>IF(PlanLayout!E39="","",PlanLayout!E39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F39" s="4">
+        <f>IF(PlanLayout!F39="","",PlanLayout!F39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G39" s="4">
+        <f>IF(PlanLayout!G39="","",PlanLayout!G39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H39" s="4">
+        <f>IF(PlanLayout!H39="","",PlanLayout!H39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I39" s="4">
+        <f>IF(PlanLayout!I39="","",PlanLayout!I39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J39" s="4">
+        <f>IF(PlanLayout!J39="","",PlanLayout!J39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K39" s="4">
+        <f>IF(PlanLayout!K39="","",PlanLayout!K39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L39" s="4">
+        <f>IF(PlanLayout!L39="","",PlanLayout!L39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M39" s="4">
+        <f>IF(PlanLayout!M39="","",PlanLayout!M39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N39" s="4">
+        <f>IF(PlanLayout!N39="","",PlanLayout!N39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O39" s="4">
+        <f>IF(PlanLayout!O39="","",PlanLayout!O39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P39" s="4">
+        <f>IF(PlanLayout!P39="","",PlanLayout!P39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q39" s="4">
+        <f>IF(PlanLayout!Q39="","",PlanLayout!Q39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R39" s="4">
+        <f>IF(PlanLayout!R39="","",PlanLayout!R39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S39" s="4">
+        <f>IF(PlanLayout!S39="","",PlanLayout!S39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T39" s="4">
+        <f>IF(PlanLayout!T39="","",PlanLayout!T39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U39" s="4">
+        <f>IF(PlanLayout!U39="","",PlanLayout!U39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V39" s="4">
+        <f>IF(PlanLayout!V39="","",PlanLayout!V39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W39" s="4">
+        <f>IF(PlanLayout!W39="","",PlanLayout!W39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X39" s="4">
+        <f>IF(PlanLayout!X39="","",PlanLayout!X39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y39" s="4">
+        <f>IF(PlanLayout!Y39="","",PlanLayout!Y39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z39" s="4">
+        <f>IF(PlanLayout!Z39="","",PlanLayout!Z39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA39" s="4">
+        <f>IF(PlanLayout!AA39="","",PlanLayout!AA39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB39" s="4">
+        <f>IF(PlanLayout!AB39="","",PlanLayout!AB39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC39" s="4">
+        <f>IF(PlanLayout!AC39="","",PlanLayout!AC39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD39" s="4">
+        <f>IF(PlanLayout!AD39="","",PlanLayout!AD39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE39" s="4">
+        <f>IF(PlanLayout!AE39="","",PlanLayout!AE39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF39" s="4">
+        <f>IF(PlanLayout!AF39="","",PlanLayout!AF39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG39" s="4">
+        <f>IF(PlanLayout!AG39="","",PlanLayout!AG39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH39" s="4">
+        <f>IF(PlanLayout!AH39="","",PlanLayout!AH39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI39" s="4">
+        <f>IF(PlanLayout!AI39="","",PlanLayout!AI39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ39" s="4">
+        <f>IF(PlanLayout!AJ39="","",PlanLayout!AJ39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK39" s="4">
+        <f>IF(PlanLayout!AK39="","",PlanLayout!AK39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL39" s="4">
+        <f>IF(PlanLayout!AL39="","",PlanLayout!AL39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM39" s="4">
+        <f>IF(PlanLayout!AM39="","",PlanLayout!AM39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN39" s="4">
+        <f>IF(PlanLayout!AN39="","",PlanLayout!AN39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO39" s="4">
+        <f>IF(PlanLayout!AO39="","",PlanLayout!AO39&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO39,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO39,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO39,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO39,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="B40" s="4">
+        <f>IF(PlanLayout!B40="","",PlanLayout!B40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C40" s="4">
+        <f>IF(PlanLayout!C40="","",PlanLayout!C40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D40" s="4">
+        <f>IF(PlanLayout!D40="","",PlanLayout!D40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E40" s="4">
+        <f>IF(PlanLayout!E40="","",PlanLayout!E40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F40" s="4">
+        <f>IF(PlanLayout!F40="","",PlanLayout!F40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G40" s="4">
+        <f>IF(PlanLayout!G40="","",PlanLayout!G40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H40" s="4">
+        <f>IF(PlanLayout!H40="","",PlanLayout!H40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I40" s="4">
+        <f>IF(PlanLayout!I40="","",PlanLayout!I40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J40" s="4">
+        <f>IF(PlanLayout!J40="","",PlanLayout!J40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K40" s="4">
+        <f>IF(PlanLayout!K40="","",PlanLayout!K40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L40" s="4">
+        <f>IF(PlanLayout!L40="","",PlanLayout!L40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M40" s="4">
+        <f>IF(PlanLayout!M40="","",PlanLayout!M40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N40" s="4">
+        <f>IF(PlanLayout!N40="","",PlanLayout!N40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O40" s="4">
+        <f>IF(PlanLayout!O40="","",PlanLayout!O40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P40" s="4">
+        <f>IF(PlanLayout!P40="","",PlanLayout!P40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q40" s="4">
+        <f>IF(PlanLayout!Q40="","",PlanLayout!Q40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R40" s="4">
+        <f>IF(PlanLayout!R40="","",PlanLayout!R40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S40" s="4">
+        <f>IF(PlanLayout!S40="","",PlanLayout!S40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T40" s="4">
+        <f>IF(PlanLayout!T40="","",PlanLayout!T40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U40" s="4">
+        <f>IF(PlanLayout!U40="","",PlanLayout!U40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V40" s="4">
+        <f>IF(PlanLayout!V40="","",PlanLayout!V40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W40" s="4">
+        <f>IF(PlanLayout!W40="","",PlanLayout!W40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X40" s="4">
+        <f>IF(PlanLayout!X40="","",PlanLayout!X40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y40" s="4">
+        <f>IF(PlanLayout!Y40="","",PlanLayout!Y40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z40" s="4">
+        <f>IF(PlanLayout!Z40="","",PlanLayout!Z40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA40" s="4">
+        <f>IF(PlanLayout!AA40="","",PlanLayout!AA40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB40" s="4">
+        <f>IF(PlanLayout!AB40="","",PlanLayout!AB40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC40" s="4">
+        <f>IF(PlanLayout!AC40="","",PlanLayout!AC40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD40" s="4">
+        <f>IF(PlanLayout!AD40="","",PlanLayout!AD40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE40" s="4">
+        <f>IF(PlanLayout!AE40="","",PlanLayout!AE40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF40" s="4">
+        <f>IF(PlanLayout!AF40="","",PlanLayout!AF40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG40" s="4">
+        <f>IF(PlanLayout!AG40="","",PlanLayout!AG40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH40" s="4">
+        <f>IF(PlanLayout!AH40="","",PlanLayout!AH40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI40" s="4">
+        <f>IF(PlanLayout!AI40="","",PlanLayout!AI40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ40" s="4">
+        <f>IF(PlanLayout!AJ40="","",PlanLayout!AJ40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK40" s="4">
+        <f>IF(PlanLayout!AK40="","",PlanLayout!AK40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL40" s="4">
+        <f>IF(PlanLayout!AL40="","",PlanLayout!AL40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM40" s="4">
+        <f>IF(PlanLayout!AM40="","",PlanLayout!AM40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN40" s="4">
+        <f>IF(PlanLayout!AN40="","",PlanLayout!AN40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO40" s="4">
+        <f>IF(PlanLayout!AO40="","",PlanLayout!AO40&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO40,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO40,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO40,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO40,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="B41" s="4">
+        <f>IF(PlanLayout!B41="","",PlanLayout!B41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!B41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="C41" s="4">
+        <f>IF(PlanLayout!C41="","",PlanLayout!C41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!C41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="D41" s="4">
+        <f>IF(PlanLayout!D41="","",PlanLayout!D41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!D41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="E41" s="4">
+        <f>IF(PlanLayout!E41="","",PlanLayout!E41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!E41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="F41" s="4">
+        <f>IF(PlanLayout!F41="","",PlanLayout!F41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!F41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="G41" s="4">
+        <f>IF(PlanLayout!G41="","",PlanLayout!G41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!G41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="H41" s="4">
+        <f>IF(PlanLayout!H41="","",PlanLayout!H41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!H41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="I41" s="4">
+        <f>IF(PlanLayout!I41="","",PlanLayout!I41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!I41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="J41" s="4">
+        <f>IF(PlanLayout!J41="","",PlanLayout!J41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!J41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="K41" s="4">
+        <f>IF(PlanLayout!K41="","",PlanLayout!K41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!K41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="L41" s="4">
+        <f>IF(PlanLayout!L41="","",PlanLayout!L41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!L41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="M41" s="4">
+        <f>IF(PlanLayout!M41="","",PlanLayout!M41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!M41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="N41" s="4">
+        <f>IF(PlanLayout!N41="","",PlanLayout!N41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!N41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="O41" s="4">
+        <f>IF(PlanLayout!O41="","",PlanLayout!O41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!O41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="P41" s="4">
+        <f>IF(PlanLayout!P41="","",PlanLayout!P41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!P41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Q41" s="4">
+        <f>IF(PlanLayout!Q41="","",PlanLayout!Q41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Q41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="R41" s="4">
+        <f>IF(PlanLayout!R41="","",PlanLayout!R41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!R41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="S41" s="4">
+        <f>IF(PlanLayout!S41="","",PlanLayout!S41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!S41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="T41" s="4">
+        <f>IF(PlanLayout!T41="","",PlanLayout!T41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!T41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="U41" s="4">
+        <f>IF(PlanLayout!U41="","",PlanLayout!U41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!U41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="V41" s="4">
+        <f>IF(PlanLayout!V41="","",PlanLayout!V41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!V41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="W41" s="4">
+        <f>IF(PlanLayout!W41="","",PlanLayout!W41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!W41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="X41" s="4">
+        <f>IF(PlanLayout!X41="","",PlanLayout!X41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!X41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Y41" s="4">
+        <f>IF(PlanLayout!Y41="","",PlanLayout!Y41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Y41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="Z41" s="4">
+        <f>IF(PlanLayout!Z41="","",PlanLayout!Z41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!Z41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AA41" s="4">
+        <f>IF(PlanLayout!AA41="","",PlanLayout!AA41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AA41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AB41" s="4">
+        <f>IF(PlanLayout!AB41="","",PlanLayout!AB41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AB41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AC41" s="4">
+        <f>IF(PlanLayout!AC41="","",PlanLayout!AC41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AC41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AD41" s="4">
+        <f>IF(PlanLayout!AD41="","",PlanLayout!AD41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AD41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AE41" s="4">
+        <f>IF(PlanLayout!AE41="","",PlanLayout!AE41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AE41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AF41" s="4">
+        <f>IF(PlanLayout!AF41="","",PlanLayout!AF41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AF41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AG41" s="4">
+        <f>IF(PlanLayout!AG41="","",PlanLayout!AG41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AG41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AH41" s="4">
+        <f>IF(PlanLayout!AH41="","",PlanLayout!AH41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AH41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AI41" s="4">
+        <f>IF(PlanLayout!AI41="","",PlanLayout!AI41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AI41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AJ41" s="4">
+        <f>IF(PlanLayout!AJ41="","",PlanLayout!AJ41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AJ41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AK41" s="4">
+        <f>IF(PlanLayout!AK41="","",PlanLayout!AK41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AK41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AL41" s="4">
+        <f>IF(PlanLayout!AL41="","",PlanLayout!AL41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AL41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AM41" s="4">
+        <f>IF(PlanLayout!AM41="","",PlanLayout!AM41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AM41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AN41" s="4">
+        <f>IF(PlanLayout!AN41="","",PlanLayout!AN41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AN41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+      <c r="AO41" s="4">
+        <f>IF(PlanLayout!AO41="","",PlanLayout!AO41&amp;CHAR(10)&amp;IFERROR(IF(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO41,tblStellplatz[Stellplatz],0))="","leer",IF(LEFT(RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO41,tblStellplatz[Stellplatz],0)),4),1)="0",RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO41,tblStellplatz[Stellplatz],0)),5),RIGHT(INDEX(tblStellplatz[SAP],MATCH(PlanLayout!AO41,tblStellplatz[Stellplatz],0)),4))),"?"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <conditionalFormatting sqref="B2:AO41">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>ISNUMBER(SEARCH("leer",B2))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>AND(B2&lt;&gt;"",NOT(ISNUMBER(SEARCH("leer",B2))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/lager-scanner/Lager_Vorlage.xlsx
+++ b/lager-scanner/Lager_Vorlage.xlsx
@@ -8,13 +8,16 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materialliste" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stellplaetze" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protokoll" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lageruebersicht" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlanLayout" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagerplan" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verpackung" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stellplaetze" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protokoll" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lageruebersicht" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlanLayout" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagerplan" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Verpackung'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -190,22 +193,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblMaterial" displayName="tblMaterial" ref="A1:F2" headerRowCount="1">
-  <autoFilter ref="A1:F2"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblMaterial" displayName="tblMaterial" ref="A1:D2" headerRowCount="1">
+  <autoFilter ref="A1:D2"/>
+  <tableColumns count="4">
     <tableColumn id="1" name="SAP"/>
     <tableColumn id="2" name="Bezeichnung"/>
     <tableColumn id="3" name="Lagerstand"/>
     <tableColumn id="4" name="Meldebestand"/>
-    <tableColumn id="5" name="StkProKarton"/>
-    <tableColumn id="6" name="StkProPalette"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblStellplatz" displayName="tblStellplatz" ref="A1:B2" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblVerpackung" displayName="tblVerpackung" ref="A1:D2" headerRowCount="1">
+  <autoFilter ref="A1:D2"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="SAP"/>
+    <tableColumn id="2" name="Bezeichnung"/>
+    <tableColumn id="3" name="StkProPalette"/>
+    <tableColumn id="4" name="StkProKarton"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblStellplatz" displayName="tblStellplatz" ref="A1:B2" headerRowCount="1">
   <autoFilter ref="A1:B2"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Stellplatz"/>
@@ -215,8 +229,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblProtokoll" displayName="tblProtokoll" ref="A1:H2" headerRowCount="1">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblProtokoll" displayName="tblProtokoll" ref="A1:H2" headerRowCount="1">
   <autoFilter ref="A1:H2"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Zeit"/>
@@ -521,15 +535,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -553,16 +565,6 @@
           <t>Meldebestand</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>StkProKarton</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>StkProPalette</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -580,12 +582,6 @@
       </c>
       <c r="D2" t="n">
         <v>10</v>
-      </c>
-      <c r="E2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F2" t="n">
-        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -597,6 +593,70 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Bezeichnung</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>StkProPalette</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>StkProKarton</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1000001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Beispielmaterial</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>480</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -635,7 +695,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -714,7 +774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26768,7 +26828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26913,7 +26973,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
